--- a/Tejas_Agrawal_Rirekisho.xlsx
+++ b/Tejas_Agrawal_Rirekisho.xlsx
@@ -9,7 +9,6 @@
   </bookViews>
   <sheets>
     <sheet name="履歴書_フォーマット" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="履歴書_記入例" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="138" uniqueCount="91">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="57">
   <si>
     <t xml:space="preserve">履 歴 書</t>
   </si>
@@ -165,6 +164,7 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">IT</t>
     </r>
@@ -174,6 +174,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">分野での</t>
     </r>
@@ -183,6 +184,7 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">MBA</t>
     </r>
@@ -192,6 +194,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">と監査業務で培った「データ分析力・論理的思考力」を持ち、実践的なプログラミング</t>
     </r>
@@ -201,6 +204,7 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">(C#, C++, MySQL, Unity)</t>
     </r>
@@ -210,6 +214,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を習得しました。
 さらに、</t>
@@ -220,6 +225,7 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">HTML/CSS/JavaScript</t>
     </r>
@@ -229,6 +235,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">を用いて自作のポートフォリオサイトをゼロから構築するなど、</t>
     </r>
@@ -238,6 +245,7 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">Web</t>
     </r>
@@ -247,6 +255,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">技術や幅広い</t>
     </r>
@@ -256,6 +265,7 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">IT</t>
     </r>
@@ -265,6 +275,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">分野へ挑戦しています。
 特定の領域にこだわらず、新しい技術を柔軟に吸収する意欲を持っています。
@@ -276,6 +287,7 @@
         <color theme="1"/>
         <rFont val="Calibri"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">IT</t>
     </r>
@@ -285,6 +297,7 @@
         <color theme="1"/>
         <rFont val="Noto Sans JP"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">全般のエンジニア・プログラマーとして貢献したいと考えております。</t>
     </r>
@@ -378,109 +391,6 @@
   <si>
     <t xml:space="preserve">1 .  鉛筆以外の黒又は青の筆記具で記入。　　2 .  数字はアラビア数字で、文字はくずさず正確に書く。
 3 .  ※印のところは、該当するものを○で囲む。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　2020年　3月　1日現在</t>
-  </si>
-  <si>
-    <t xml:space="preserve">すみす　じょん</t>
-  </si>
-  <si>
-    <t xml:space="preserve">株式会社ニッポンテック　入社</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Smith John</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　ITソリューション事業部　プロジェクトマネージャー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　　以上</t>
-  </si>
-  <si>
-    <t xml:space="preserve">アメリカ合衆国</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1985年　1月 1日生（満35歳）　</t>
-  </si>
-  <si>
-    <t xml:space="preserve">男　・　女</t>
-  </si>
-  <si>
-    <t xml:space="preserve">とうきょうとちよだくかんだすだちょう</t>
-  </si>
-  <si>
-    <t xml:space="preserve">090-0000-0000</t>
-  </si>
-  <si>
-    <t xml:space="preserve">〒101-0041</t>
-  </si>
-  <si>
-    <t xml:space="preserve">東京都千代田区神田須田町2-5 ジータレントアパート301</t>
-  </si>
-  <si>
-    <t xml:space="preserve">gtalent1234@gtalent.jp</t>
-  </si>
-  <si>
-    <t xml:space="preserve">JLPT N2試験合格</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　　　　　　　　　同上</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　　　　　　　　　　　　　　　　　　　　学歴</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ニューヨーク州立ニューヨーク高等学校　卒業</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ワシントン州立ワシントン大学　IT学部　入学</t>
-  </si>
-  <si>
-    <t xml:space="preserve">2007年3月まで日本の令和大学に１年間交換留学で日本語を勉強</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ワシントン州立ワシントン大学　IT学部　卒業</t>
-  </si>
-  <si>
-    <t xml:space="preserve">フロントエンドからバックエンドまでフルスタックエンジニアとして開発経験、プロジェクトやプロダクトのマネジメント経験までの幅広い経験を御社でも発揮したいと持っております。
-2017年4月に日本語N2試験に合格しており、社内のコミュニケーションにおいては日本語は問題ございません。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　　    約　0時間　　45分</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　　　　　　　　　　　　　　　　　　　　職歴</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　　　　　　　3　　　人</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Bizmates. Incにシステムエンジニア職のインターンとして入社（2007年6月まで）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">株式会社ジータレント　入社</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　タレントソリューション事業部　システムエンジニア職</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　新規事業開発部　BizDevチームリーダー</t>
-  </si>
-  <si>
-    <t xml:space="preserve">貴社の規定に従います。</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　一身上の都合により退社</t>
-  </si>
-  <si>
-    <t xml:space="preserve">BIZGIT Inc, 入社</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　オンライン英会話事業部　プロダクトマネージャー職</t>
-  </si>
-  <si>
-    <t xml:space="preserve">フリーランスとして複数のシステム開発プロジェクトに携わる</t>
   </si>
 </sst>
 </file>
@@ -575,12 +485,14 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Noto Sans JP"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="8"/>
@@ -616,7 +528,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="34">
+  <borders count="33">
     <border diagonalUp="false" diagonalDown="false">
       <left/>
       <right/>
@@ -848,13 +760,6 @@
       <bottom/>
       <diagonal/>
     </border>
-    <border diagonalUp="false" diagonalDown="false">
-      <left style="hair"/>
-      <right style="thin"/>
-      <top style="double"/>
-      <bottom style="hair"/>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="21">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -884,7 +789,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="67">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1151,14 +1056,6 @@
     </xf>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="33" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
   </cellXfs>
@@ -1185,9 +1082,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>557640</xdr:colOff>
+      <xdr:colOff>557280</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>62640</xdr:rowOff>
+      <xdr:rowOff>62280</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1197,7 +1094,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6285240" y="177840"/>
-          <a:ext cx="1380600" cy="1780200"/>
+          <a:ext cx="1380240" cy="1779840"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1596,9 +1493,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>577440</xdr:colOff>
+      <xdr:colOff>577080</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>93960</xdr:rowOff>
+      <xdr:rowOff>93600</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1612,7 +1509,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6268680" y="144720"/>
-          <a:ext cx="1416960" cy="1844640"/>
+          <a:ext cx="1416600" cy="1844280"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1623,575 +1520,6 @@
         </a:ln>
       </xdr:spPr>
     </xdr:pic>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-</xdr:wsDr>
-</file>
-
-<file path=xl/drawings/drawing2.xml><?xml version="1.0" encoding="utf-8"?>
-<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <xdr:twoCellAnchor editAs="twoCell">
-    <xdr:from>
-      <xdr:col>10</xdr:col>
-      <xdr:colOff>340200</xdr:colOff>
-      <xdr:row>0</xdr:row>
-      <xdr:rowOff>177840</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>12</xdr:col>
-      <xdr:colOff>557640</xdr:colOff>
-      <xdr:row>11</xdr:row>
-      <xdr:rowOff>62640</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="3" name="テキスト ボックス 1"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6277320" y="177840"/>
-          <a:ext cx="1405080" cy="1780200"/>
-        </a:xfrm>
-        <a:prstGeom prst="rect">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:solidFill>
-          <a:srgbClr val="FFFFFF"/>
-        </a:solidFill>
-        <a:ln w="6350">
-          <a:solidFill>
-            <a:srgbClr val="808080"/>
-          </a:solidFill>
-          <a:prstDash val="sysDash"/>
-          <a:round/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="0"/>
-        <a:fillRef idx="0"/>
-        <a:effectRef idx="0"/>
-        <a:fontRef idx="minor"/>
-      </xdr:style>
-      <xdr:txBody>
-        <a:bodyPr horzOverflow="clip" vertOverflow="clip" lIns="90000" tIns="45000" rIns="90000" bIns="45000" anchor="t">
-          <a:noAutofit/>
-        </a:bodyPr>
-        <a:p>
-          <a:pPr>
-            <a:lnSpc>
-              <a:spcPts val="700"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:endParaRPr lang="en-IN" sz="1000" b="0" u="none" strike="noStrike">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Noto Serif JP"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr>
-            <a:lnSpc>
-              <a:spcPts val="700"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="ja-JP" sz="900" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="ＭＳ 明朝"/>
-              <a:ea typeface="ＭＳ 明朝"/>
-            </a:rPr>
-            <a:t>　　                                 </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-IN" sz="900" b="0" u="none" strike="noStrike">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Noto Serif JP"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr>
-            <a:lnSpc>
-              <a:spcPts val="850"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="900" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="ＭＳ 明朝"/>
-              <a:ea typeface="ＭＳ 明朝"/>
-            </a:rPr>
-            <a:t>   写真をはる位置</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-IN" sz="900" b="0" u="none" strike="noStrike">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Noto Serif JP"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr>
-            <a:lnSpc>
-              <a:spcPts val="850"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:endParaRPr lang="en-IN" sz="900" b="0" u="none" strike="noStrike">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Noto Serif JP"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr>
-            <a:lnSpc>
-              <a:spcPts val="850"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="900" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="ＭＳ 明朝"/>
-              <a:ea typeface="ＭＳ 明朝"/>
-            </a:rPr>
-            <a:t>  写真をはる必要が </a:t>
-          </a:r>
-          <a:endParaRPr lang="en-IN" sz="900" b="0" u="none" strike="noStrike">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Noto Serif JP"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr>
-            <a:lnSpc>
-              <a:spcPts val="850"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="900" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="ＭＳ 明朝"/>
-              <a:ea typeface="ＭＳ 明朝"/>
-            </a:rPr>
-            <a:t>  ある場合</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-IN" sz="900" b="0" u="none" strike="noStrike">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Noto Serif JP"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr>
-            <a:lnSpc>
-              <a:spcPts val="850"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="900" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="ＭＳ 明朝"/>
-              <a:ea typeface="ＭＳ 明朝"/>
-            </a:rPr>
-            <a:t> 1</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" sz="900" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="ＭＳ 明朝"/>
-              <a:ea typeface="ＭＳ 明朝"/>
-            </a:rPr>
-            <a:t>．縦  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="900" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="ＭＳ 明朝"/>
-              <a:ea typeface="ＭＳ 明朝"/>
-            </a:rPr>
-            <a:t>36</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" sz="900" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="ＭＳ 明朝"/>
-              <a:ea typeface="ＭＳ 明朝"/>
-            </a:rPr>
-            <a:t>～</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="900" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="ＭＳ 明朝"/>
-              <a:ea typeface="ＭＳ 明朝"/>
-            </a:rPr>
-            <a:t>40mm</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-IN" sz="900" b="0" u="none" strike="noStrike">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Noto Serif JP"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr>
-            <a:lnSpc>
-              <a:spcPts val="850"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="900" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="ＭＳ 明朝"/>
-              <a:ea typeface="ＭＳ 明朝"/>
-            </a:rPr>
-            <a:t>    横  </a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="900" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="ＭＳ 明朝"/>
-              <a:ea typeface="ＭＳ 明朝"/>
-            </a:rPr>
-            <a:t>24</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" sz="900" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="ＭＳ 明朝"/>
-              <a:ea typeface="ＭＳ 明朝"/>
-            </a:rPr>
-            <a:t>～</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="en-US" sz="900" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="ＭＳ 明朝"/>
-              <a:ea typeface="ＭＳ 明朝"/>
-            </a:rPr>
-            <a:t>30mm</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" sz="900" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="ＭＳ 明朝"/>
-              <a:ea typeface="ＭＳ 明朝"/>
-            </a:rPr>
-            <a:t>　</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-IN" sz="900" b="0" u="none" strike="noStrike">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Noto Serif JP"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr>
-            <a:lnSpc>
-              <a:spcPts val="850"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="900" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="ＭＳ 明朝"/>
-              <a:ea typeface="ＭＳ 明朝"/>
-            </a:rPr>
-            <a:t> 2.</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" sz="900" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="ＭＳ 明朝"/>
-              <a:ea typeface="ＭＳ 明朝"/>
-            </a:rPr>
-            <a:t>本人単身胸から上</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-IN" sz="900" b="0" u="none" strike="noStrike">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Noto Serif JP"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr>
-            <a:lnSpc>
-              <a:spcPts val="850"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:r>
-            <a:rPr lang="en-US" sz="900" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="ＭＳ 明朝"/>
-              <a:ea typeface="ＭＳ 明朝"/>
-            </a:rPr>
-            <a:t> 3.</a:t>
-          </a:r>
-          <a:r>
-            <a:rPr lang="ja-JP" sz="900" b="0" u="none" strike="noStrike">
-              <a:solidFill>
-                <a:schemeClr val="dk1"/>
-              </a:solidFill>
-              <a:effectLst/>
-              <a:uFillTx/>
-              <a:latin typeface="ＭＳ 明朝"/>
-              <a:ea typeface="ＭＳ 明朝"/>
-            </a:rPr>
-            <a:t>裏面のりづけ</a:t>
-          </a:r>
-          <a:endParaRPr lang="en-IN" sz="900" b="0" u="none" strike="noStrike">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Noto Serif JP"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr>
-            <a:lnSpc>
-              <a:spcPts val="1100"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:endParaRPr lang="en-IN" sz="900" b="0" u="none" strike="noStrike">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Noto Serif JP"/>
-          </a:endParaRPr>
-        </a:p>
-        <a:p>
-          <a:pPr>
-            <a:lnSpc>
-              <a:spcPts val="1001"/>
-            </a:lnSpc>
-          </a:pPr>
-          <a:endParaRPr lang="en-IN" sz="900" b="0" u="none" strike="noStrike">
-            <a:effectLst/>
-            <a:uFillTx/>
-            <a:latin typeface="Noto Serif JP"/>
-          </a:endParaRPr>
-        </a:p>
-      </xdr:txBody>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="twoCell">
-    <xdr:from>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>170280</xdr:colOff>
-      <xdr:row>12</xdr:row>
-      <xdr:rowOff>60840</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>11</xdr:col>
-      <xdr:colOff>481680</xdr:colOff>
-      <xdr:row>13</xdr:row>
-      <xdr:rowOff>125640</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="4" name="楕円 2"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="6701400" y="2118240"/>
-          <a:ext cx="311400" cy="226800"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor"/>
-      </xdr:style>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="twoCell">
-    <xdr:from>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>203040</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>63360</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>23</xdr:col>
-      <xdr:colOff>514440</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>102960</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="5" name="楕円 2"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="13858560" y="8007120"/>
-          <a:ext cx="311400" cy="230040"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor"/>
-      </xdr:style>
-    </xdr:sp>
-    <xdr:clientData/>
-  </xdr:twoCellAnchor>
-  <xdr:twoCellAnchor editAs="twoCell">
-    <xdr:from>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>88920</xdr:colOff>
-      <xdr:row>45</xdr:row>
-      <xdr:rowOff>50760</xdr:rowOff>
-    </xdr:from>
-    <xdr:to>
-      <xdr:col>26</xdr:col>
-      <xdr:colOff>400320</xdr:colOff>
-      <xdr:row>46</xdr:row>
-      <xdr:rowOff>90360</xdr:rowOff>
-    </xdr:to>
-    <xdr:sp>
-      <xdr:nvSpPr>
-        <xdr:cNvPr id="6" name="楕円 2"/>
-        <xdr:cNvSpPr/>
-      </xdr:nvSpPr>
-      <xdr:spPr>
-        <a:xfrm>
-          <a:off x="15525720" y="7994520"/>
-          <a:ext cx="311400" cy="230040"/>
-        </a:xfrm>
-        <a:prstGeom prst="ellipse">
-          <a:avLst/>
-        </a:prstGeom>
-        <a:noFill/>
-        <a:ln w="9525">
-          <a:solidFill>
-            <a:srgbClr val="000000"/>
-          </a:solidFill>
-          <a:round/>
-        </a:ln>
-      </xdr:spPr>
-      <xdr:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1">
-            <a:shade val="50000"/>
-          </a:schemeClr>
-        </a:lnRef>
-        <a:fillRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor"/>
-      </xdr:style>
-    </xdr:sp>
     <xdr:clientData/>
   </xdr:twoCellAnchor>
 </xdr:wsDr>
@@ -4612,2160 +3940,4 @@
   </headerFooter>
   <drawing r:id="rId2"/>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="true"/>
-  </sheetPr>
-  <dimension ref="A1:AA65"/>
-  <sheetFormatPr defaultColWidth="8.83984375" defaultRowHeight="18.75" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="27" min="1" style="1" width="8.5"/>
-    <col collapsed="false" customWidth="false" hidden="false" outlineLevel="0" max="16384" min="28" style="1" width="8.84"/>
-  </cols>
-  <sheetData>
-    <row r="1" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="2"/>
-      <c r="B1" s="2"/>
-      <c r="C1" s="2"/>
-      <c r="D1" s="3"/>
-      <c r="E1" s="4"/>
-      <c r="F1" s="4"/>
-      <c r="G1" s="4"/>
-      <c r="H1" s="4"/>
-      <c r="I1" s="4"/>
-      <c r="J1" s="4"/>
-      <c r="K1" s="3"/>
-      <c r="L1" s="3"/>
-      <c r="M1" s="3"/>
-      <c r="O1" s="3"/>
-      <c r="P1" s="3"/>
-      <c r="Q1" s="3"/>
-      <c r="R1" s="3"/>
-      <c r="S1" s="3"/>
-      <c r="T1" s="3"/>
-      <c r="U1" s="3"/>
-      <c r="V1" s="3"/>
-      <c r="W1" s="3"/>
-      <c r="X1" s="3"/>
-      <c r="Y1" s="3"/>
-      <c r="Z1" s="3"/>
-      <c r="AA1" s="3"/>
-    </row>
-    <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="5" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="5"/>
-      <c r="C2" s="5"/>
-      <c r="D2" s="3"/>
-      <c r="E2" s="6"/>
-      <c r="F2" s="6"/>
-      <c r="G2" s="6"/>
-      <c r="H2" s="6"/>
-      <c r="I2" s="6"/>
-      <c r="J2" s="6"/>
-      <c r="K2" s="3"/>
-      <c r="L2" s="3"/>
-      <c r="M2" s="3"/>
-      <c r="O2" s="7"/>
-      <c r="P2" s="7"/>
-      <c r="Q2" s="7"/>
-      <c r="R2" s="7"/>
-      <c r="S2" s="7"/>
-      <c r="T2" s="7"/>
-      <c r="U2" s="7"/>
-      <c r="V2" s="7"/>
-      <c r="W2" s="7"/>
-      <c r="X2" s="7"/>
-      <c r="Y2" s="7"/>
-      <c r="Z2" s="7"/>
-      <c r="AA2" s="7"/>
-    </row>
-    <row r="3" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A3" s="5"/>
-      <c r="B3" s="5"/>
-      <c r="C3" s="5"/>
-      <c r="D3" s="3"/>
-      <c r="E3" s="6" t="s">
-        <v>57</v>
-      </c>
-      <c r="F3" s="6"/>
-      <c r="G3" s="6"/>
-      <c r="H3" s="6"/>
-      <c r="I3" s="6"/>
-      <c r="J3" s="6"/>
-      <c r="K3" s="3"/>
-      <c r="L3" s="3"/>
-      <c r="M3" s="3"/>
-      <c r="O3" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="P3" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q3" s="10" t="s">
-        <v>4</v>
-      </c>
-      <c r="R3" s="10"/>
-      <c r="S3" s="10"/>
-      <c r="T3" s="10"/>
-      <c r="U3" s="10"/>
-      <c r="V3" s="10"/>
-      <c r="W3" s="10"/>
-      <c r="X3" s="10"/>
-      <c r="Y3" s="10"/>
-      <c r="Z3" s="10"/>
-      <c r="AA3" s="10"/>
-    </row>
-    <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="11"/>
-      <c r="B4" s="11"/>
-      <c r="C4" s="11"/>
-      <c r="D4" s="3"/>
-      <c r="E4" s="6"/>
-      <c r="F4" s="6"/>
-      <c r="G4" s="6"/>
-      <c r="H4" s="6"/>
-      <c r="I4" s="6"/>
-      <c r="J4" s="6"/>
-      <c r="K4" s="3"/>
-      <c r="L4" s="3"/>
-      <c r="M4" s="3"/>
-      <c r="O4" s="8"/>
-      <c r="P4" s="9"/>
-      <c r="Q4" s="10"/>
-      <c r="R4" s="10"/>
-      <c r="S4" s="10"/>
-      <c r="T4" s="10"/>
-      <c r="U4" s="10"/>
-      <c r="V4" s="10"/>
-      <c r="W4" s="10"/>
-      <c r="X4" s="10"/>
-      <c r="Y4" s="10"/>
-      <c r="Z4" s="10"/>
-      <c r="AA4" s="10"/>
-    </row>
-    <row r="5" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B5" s="13" t="s">
-        <v>58</v>
-      </c>
-      <c r="C5" s="13"/>
-      <c r="D5" s="13"/>
-      <c r="E5" s="13"/>
-      <c r="F5" s="13"/>
-      <c r="G5" s="13"/>
-      <c r="H5" s="13"/>
-      <c r="I5" s="13"/>
-      <c r="J5" s="13"/>
-      <c r="K5" s="3"/>
-      <c r="L5" s="3"/>
-      <c r="M5" s="3"/>
-      <c r="O5" s="14" t="n">
-        <v>2018</v>
-      </c>
-      <c r="P5" s="15" t="n">
-        <v>12</v>
-      </c>
-      <c r="Q5" s="16" t="s">
-        <v>59</v>
-      </c>
-      <c r="R5" s="16"/>
-      <c r="S5" s="16"/>
-      <c r="T5" s="16"/>
-      <c r="U5" s="16"/>
-      <c r="V5" s="16"/>
-      <c r="W5" s="16"/>
-      <c r="X5" s="16"/>
-      <c r="Y5" s="16"/>
-      <c r="Z5" s="16"/>
-      <c r="AA5" s="16"/>
-    </row>
-    <row r="6" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="12"/>
-      <c r="B6" s="13"/>
-      <c r="C6" s="13"/>
-      <c r="D6" s="13"/>
-      <c r="E6" s="13"/>
-      <c r="F6" s="13"/>
-      <c r="G6" s="13"/>
-      <c r="H6" s="13"/>
-      <c r="I6" s="13"/>
-      <c r="J6" s="13"/>
-      <c r="K6" s="3"/>
-      <c r="L6" s="3"/>
-      <c r="M6" s="3"/>
-      <c r="O6" s="14"/>
-      <c r="P6" s="15"/>
-      <c r="Q6" s="16"/>
-      <c r="R6" s="16"/>
-      <c r="S6" s="16"/>
-      <c r="T6" s="16"/>
-      <c r="U6" s="16"/>
-      <c r="V6" s="16"/>
-      <c r="W6" s="16"/>
-      <c r="X6" s="16"/>
-      <c r="Y6" s="16"/>
-      <c r="Z6" s="16"/>
-      <c r="AA6" s="16"/>
-    </row>
-    <row r="7" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="17" t="s">
-        <v>7</v>
-      </c>
-      <c r="B7" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="C7" s="18"/>
-      <c r="D7" s="18"/>
-      <c r="E7" s="18"/>
-      <c r="F7" s="18"/>
-      <c r="G7" s="18"/>
-      <c r="H7" s="18"/>
-      <c r="I7" s="18"/>
-      <c r="J7" s="18"/>
-      <c r="K7" s="3"/>
-      <c r="L7" s="3"/>
-      <c r="M7" s="3"/>
-      <c r="O7" s="14"/>
-      <c r="P7" s="15"/>
-      <c r="Q7" s="16" t="s">
-        <v>61</v>
-      </c>
-      <c r="R7" s="16"/>
-      <c r="S7" s="16"/>
-      <c r="T7" s="16"/>
-      <c r="U7" s="16"/>
-      <c r="V7" s="16"/>
-      <c r="W7" s="16"/>
-      <c r="X7" s="16"/>
-      <c r="Y7" s="16"/>
-      <c r="Z7" s="16"/>
-      <c r="AA7" s="16"/>
-    </row>
-    <row r="8" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="17"/>
-      <c r="B8" s="18"/>
-      <c r="C8" s="18"/>
-      <c r="D8" s="18"/>
-      <c r="E8" s="18"/>
-      <c r="F8" s="18"/>
-      <c r="G8" s="18"/>
-      <c r="H8" s="18"/>
-      <c r="I8" s="18"/>
-      <c r="J8" s="18"/>
-      <c r="K8" s="3"/>
-      <c r="L8" s="3"/>
-      <c r="M8" s="3"/>
-      <c r="O8" s="14"/>
-      <c r="P8" s="15"/>
-      <c r="Q8" s="16"/>
-      <c r="R8" s="16"/>
-      <c r="S8" s="16"/>
-      <c r="T8" s="16"/>
-      <c r="U8" s="16"/>
-      <c r="V8" s="16"/>
-      <c r="W8" s="16"/>
-      <c r="X8" s="16"/>
-      <c r="Y8" s="16"/>
-      <c r="Z8" s="16"/>
-      <c r="AA8" s="16"/>
-    </row>
-    <row r="9" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="17"/>
-      <c r="B9" s="18"/>
-      <c r="C9" s="18"/>
-      <c r="D9" s="18"/>
-      <c r="E9" s="18"/>
-      <c r="F9" s="18"/>
-      <c r="G9" s="18"/>
-      <c r="H9" s="18"/>
-      <c r="I9" s="18"/>
-      <c r="J9" s="18"/>
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
-      <c r="O9" s="14"/>
-      <c r="P9" s="15"/>
-      <c r="Q9" s="16" t="s">
-        <v>53</v>
-      </c>
-      <c r="R9" s="16"/>
-      <c r="S9" s="16"/>
-      <c r="T9" s="16"/>
-      <c r="U9" s="16"/>
-      <c r="V9" s="16"/>
-      <c r="W9" s="16"/>
-      <c r="X9" s="16"/>
-      <c r="Y9" s="16"/>
-      <c r="Z9" s="16"/>
-      <c r="AA9" s="16"/>
-    </row>
-    <row r="10" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17"/>
-      <c r="B10" s="18"/>
-      <c r="C10" s="18"/>
-      <c r="D10" s="18"/>
-      <c r="E10" s="18"/>
-      <c r="F10" s="18"/>
-      <c r="G10" s="18"/>
-      <c r="H10" s="18"/>
-      <c r="I10" s="18"/>
-      <c r="J10" s="18"/>
-      <c r="K10" s="3"/>
-      <c r="L10" s="3"/>
-      <c r="M10" s="3"/>
-      <c r="O10" s="14"/>
-      <c r="P10" s="15"/>
-      <c r="Q10" s="16"/>
-      <c r="R10" s="16"/>
-      <c r="S10" s="16"/>
-      <c r="T10" s="16"/>
-      <c r="U10" s="16"/>
-      <c r="V10" s="16"/>
-      <c r="W10" s="16"/>
-      <c r="X10" s="16"/>
-      <c r="Y10" s="16"/>
-      <c r="Z10" s="16"/>
-      <c r="AA10" s="16"/>
-    </row>
-    <row r="11" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="17"/>
-      <c r="B11" s="18"/>
-      <c r="C11" s="18"/>
-      <c r="D11" s="18"/>
-      <c r="E11" s="18"/>
-      <c r="F11" s="18"/>
-      <c r="G11" s="18"/>
-      <c r="H11" s="18"/>
-      <c r="I11" s="18"/>
-      <c r="J11" s="18"/>
-      <c r="K11" s="3"/>
-      <c r="L11" s="3"/>
-      <c r="M11" s="3"/>
-      <c r="O11" s="14"/>
-      <c r="P11" s="15"/>
-      <c r="Q11" s="16" t="s">
-        <v>62</v>
-      </c>
-      <c r="R11" s="16"/>
-      <c r="S11" s="16"/>
-      <c r="T11" s="16"/>
-      <c r="U11" s="16"/>
-      <c r="V11" s="16"/>
-      <c r="W11" s="16"/>
-      <c r="X11" s="16"/>
-      <c r="Y11" s="16"/>
-      <c r="Z11" s="16"/>
-      <c r="AA11" s="16"/>
-    </row>
-    <row r="12" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="17"/>
-      <c r="B12" s="18"/>
-      <c r="C12" s="18"/>
-      <c r="D12" s="18"/>
-      <c r="E12" s="18"/>
-      <c r="F12" s="18"/>
-      <c r="G12" s="18"/>
-      <c r="H12" s="18"/>
-      <c r="I12" s="18"/>
-      <c r="J12" s="18"/>
-      <c r="K12" s="3"/>
-      <c r="L12" s="3"/>
-      <c r="M12" s="3"/>
-      <c r="O12" s="14"/>
-      <c r="P12" s="15"/>
-      <c r="Q12" s="16"/>
-      <c r="R12" s="16"/>
-      <c r="S12" s="16"/>
-      <c r="T12" s="16"/>
-      <c r="U12" s="16"/>
-      <c r="V12" s="16"/>
-      <c r="W12" s="16"/>
-      <c r="X12" s="16"/>
-      <c r="Y12" s="16"/>
-      <c r="Z12" s="16"/>
-      <c r="AA12" s="16"/>
-    </row>
-    <row r="13" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="19" t="s">
-        <v>9</v>
-      </c>
-      <c r="B13" s="20" t="s">
-        <v>63</v>
-      </c>
-      <c r="C13" s="20"/>
-      <c r="D13" s="20"/>
-      <c r="E13" s="19" t="s">
-        <v>11</v>
-      </c>
-      <c r="F13" s="19"/>
-      <c r="G13" s="21" t="s">
-        <v>64</v>
-      </c>
-      <c r="H13" s="21"/>
-      <c r="I13" s="21"/>
-      <c r="J13" s="21"/>
-      <c r="K13" s="22" t="s">
-        <v>13</v>
-      </c>
-      <c r="L13" s="23" t="s">
-        <v>65</v>
-      </c>
-      <c r="M13" s="23"/>
-      <c r="O13" s="14"/>
-      <c r="P13" s="15"/>
-      <c r="Q13" s="16"/>
-      <c r="R13" s="16"/>
-      <c r="S13" s="16"/>
-      <c r="T13" s="16"/>
-      <c r="U13" s="16"/>
-      <c r="V13" s="16"/>
-      <c r="W13" s="16"/>
-      <c r="X13" s="16"/>
-      <c r="Y13" s="16"/>
-      <c r="Z13" s="16"/>
-      <c r="AA13" s="16"/>
-    </row>
-    <row r="14" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="19"/>
-      <c r="B14" s="20"/>
-      <c r="C14" s="20"/>
-      <c r="D14" s="20"/>
-      <c r="E14" s="19"/>
-      <c r="F14" s="19"/>
-      <c r="G14" s="21"/>
-      <c r="H14" s="21"/>
-      <c r="I14" s="21"/>
-      <c r="J14" s="21"/>
-      <c r="K14" s="22"/>
-      <c r="L14" s="23"/>
-      <c r="M14" s="23"/>
-      <c r="O14" s="14"/>
-      <c r="P14" s="15"/>
-      <c r="Q14" s="16"/>
-      <c r="R14" s="16"/>
-      <c r="S14" s="16"/>
-      <c r="T14" s="16"/>
-      <c r="U14" s="16"/>
-      <c r="V14" s="16"/>
-      <c r="W14" s="16"/>
-      <c r="X14" s="16"/>
-      <c r="Y14" s="16"/>
-      <c r="Z14" s="16"/>
-      <c r="AA14" s="16"/>
-    </row>
-    <row r="15" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="24" t="s">
-        <v>5</v>
-      </c>
-      <c r="B15" s="25" t="s">
-        <v>66</v>
-      </c>
-      <c r="C15" s="25"/>
-      <c r="D15" s="25"/>
-      <c r="E15" s="25"/>
-      <c r="F15" s="25"/>
-      <c r="G15" s="25"/>
-      <c r="H15" s="25"/>
-      <c r="I15" s="25"/>
-      <c r="J15" s="25"/>
-      <c r="K15" s="26" t="s">
-        <v>16</v>
-      </c>
-      <c r="L15" s="26"/>
-      <c r="M15" s="26"/>
-      <c r="O15" s="14"/>
-      <c r="P15" s="15"/>
-      <c r="Q15" s="16"/>
-      <c r="R15" s="16"/>
-      <c r="S15" s="16"/>
-      <c r="T15" s="16"/>
-      <c r="U15" s="16"/>
-      <c r="V15" s="16"/>
-      <c r="W15" s="16"/>
-      <c r="X15" s="16"/>
-      <c r="Y15" s="16"/>
-      <c r="Z15" s="16"/>
-      <c r="AA15" s="16"/>
-    </row>
-    <row r="16" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="24"/>
-      <c r="B16" s="25"/>
-      <c r="C16" s="25"/>
-      <c r="D16" s="25"/>
-      <c r="E16" s="25"/>
-      <c r="F16" s="25"/>
-      <c r="G16" s="25"/>
-      <c r="H16" s="25"/>
-      <c r="I16" s="25"/>
-      <c r="J16" s="25"/>
-      <c r="K16" s="27" t="s">
-        <v>67</v>
-      </c>
-      <c r="L16" s="27"/>
-      <c r="M16" s="27"/>
-      <c r="N16" s="28"/>
-      <c r="O16" s="14"/>
-      <c r="P16" s="15"/>
-      <c r="Q16" s="16"/>
-      <c r="R16" s="16"/>
-      <c r="S16" s="16"/>
-      <c r="T16" s="16"/>
-      <c r="U16" s="16"/>
-      <c r="V16" s="16"/>
-      <c r="W16" s="16"/>
-      <c r="X16" s="16"/>
-      <c r="Y16" s="16"/>
-      <c r="Z16" s="16"/>
-      <c r="AA16" s="16"/>
-    </row>
-    <row r="17" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="29" t="s">
-        <v>17</v>
-      </c>
-      <c r="B17" s="30" t="s">
-        <v>68</v>
-      </c>
-      <c r="C17" s="30"/>
-      <c r="D17" s="30"/>
-      <c r="E17" s="30"/>
-      <c r="F17" s="30"/>
-      <c r="G17" s="30"/>
-      <c r="H17" s="30"/>
-      <c r="I17" s="30"/>
-      <c r="J17" s="30"/>
-      <c r="K17" s="27"/>
-      <c r="L17" s="27"/>
-      <c r="M17" s="27"/>
-      <c r="N17" s="28"/>
-      <c r="O17" s="14"/>
-      <c r="P17" s="15"/>
-      <c r="Q17" s="16"/>
-      <c r="R17" s="16"/>
-      <c r="S17" s="16"/>
-      <c r="T17" s="16"/>
-      <c r="U17" s="16"/>
-      <c r="V17" s="16"/>
-      <c r="W17" s="16"/>
-      <c r="X17" s="16"/>
-      <c r="Y17" s="16"/>
-      <c r="Z17" s="16"/>
-      <c r="AA17" s="16"/>
-    </row>
-    <row r="18" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="29"/>
-      <c r="B18" s="30"/>
-      <c r="C18" s="30"/>
-      <c r="D18" s="30"/>
-      <c r="E18" s="30"/>
-      <c r="F18" s="30"/>
-      <c r="G18" s="30"/>
-      <c r="H18" s="30"/>
-      <c r="I18" s="30"/>
-      <c r="J18" s="30"/>
-      <c r="K18" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="L18" s="31"/>
-      <c r="M18" s="31"/>
-      <c r="O18" s="14"/>
-      <c r="P18" s="15"/>
-      <c r="Q18" s="16"/>
-      <c r="R18" s="16"/>
-      <c r="S18" s="16"/>
-      <c r="T18" s="16"/>
-      <c r="U18" s="16"/>
-      <c r="V18" s="16"/>
-      <c r="W18" s="16"/>
-      <c r="X18" s="16"/>
-      <c r="Y18" s="16"/>
-      <c r="Z18" s="16"/>
-      <c r="AA18" s="16"/>
-    </row>
-    <row r="19" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="29"/>
-      <c r="B19" s="32" t="s">
-        <v>69</v>
-      </c>
-      <c r="C19" s="32"/>
-      <c r="D19" s="32"/>
-      <c r="E19" s="32"/>
-      <c r="F19" s="32"/>
-      <c r="G19" s="32"/>
-      <c r="H19" s="32"/>
-      <c r="I19" s="32"/>
-      <c r="J19" s="32"/>
-      <c r="K19" s="33" t="s">
-        <v>70</v>
-      </c>
-      <c r="L19" s="33"/>
-      <c r="M19" s="33"/>
-      <c r="O19" s="34"/>
-      <c r="P19" s="35"/>
-      <c r="Q19" s="36"/>
-      <c r="R19" s="36"/>
-      <c r="S19" s="36"/>
-      <c r="T19" s="36"/>
-      <c r="U19" s="36"/>
-      <c r="V19" s="36"/>
-      <c r="W19" s="36"/>
-      <c r="X19" s="36"/>
-      <c r="Y19" s="36"/>
-      <c r="Z19" s="36"/>
-      <c r="AA19" s="36"/>
-    </row>
-    <row r="20" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="29"/>
-      <c r="B20" s="32"/>
-      <c r="C20" s="32"/>
-      <c r="D20" s="32"/>
-      <c r="E20" s="32"/>
-      <c r="F20" s="32"/>
-      <c r="G20" s="32"/>
-      <c r="H20" s="32"/>
-      <c r="I20" s="32"/>
-      <c r="J20" s="32"/>
-      <c r="K20" s="33"/>
-      <c r="L20" s="33"/>
-      <c r="M20" s="33"/>
-      <c r="O20" s="34"/>
-      <c r="P20" s="35"/>
-      <c r="Q20" s="36"/>
-      <c r="R20" s="36"/>
-      <c r="S20" s="36"/>
-      <c r="T20" s="36"/>
-      <c r="U20" s="36"/>
-      <c r="V20" s="36"/>
-      <c r="W20" s="36"/>
-      <c r="X20" s="36"/>
-      <c r="Y20" s="36"/>
-      <c r="Z20" s="36"/>
-      <c r="AA20" s="36"/>
-    </row>
-    <row r="21" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="12" t="s">
-        <v>5</v>
-      </c>
-      <c r="B21" s="37"/>
-      <c r="C21" s="37"/>
-      <c r="D21" s="37"/>
-      <c r="E21" s="37"/>
-      <c r="F21" s="37"/>
-      <c r="G21" s="37"/>
-      <c r="H21" s="37"/>
-      <c r="I21" s="37"/>
-      <c r="J21" s="37"/>
-      <c r="K21" s="31" t="s">
-        <v>16</v>
-      </c>
-      <c r="L21" s="31"/>
-      <c r="M21" s="31"/>
-      <c r="O21" s="38"/>
-      <c r="P21" s="38"/>
-      <c r="Q21" s="38"/>
-      <c r="R21" s="38"/>
-      <c r="S21" s="38"/>
-      <c r="T21" s="38"/>
-      <c r="U21" s="38"/>
-      <c r="V21" s="38"/>
-      <c r="W21" s="38"/>
-      <c r="X21" s="38"/>
-      <c r="Y21" s="38"/>
-      <c r="Z21" s="38"/>
-      <c r="AA21" s="38"/>
-    </row>
-    <row r="22" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="12"/>
-      <c r="B22" s="37"/>
-      <c r="C22" s="37"/>
-      <c r="D22" s="37"/>
-      <c r="E22" s="37"/>
-      <c r="F22" s="37"/>
-      <c r="G22" s="37"/>
-      <c r="H22" s="37"/>
-      <c r="I22" s="37"/>
-      <c r="J22" s="37"/>
-      <c r="K22" s="27"/>
-      <c r="L22" s="27"/>
-      <c r="M22" s="27"/>
-      <c r="O22" s="8" t="s">
-        <v>2</v>
-      </c>
-      <c r="P22" s="9" t="s">
-        <v>3</v>
-      </c>
-      <c r="Q22" s="39" t="s">
-        <v>22</v>
-      </c>
-      <c r="R22" s="39"/>
-      <c r="S22" s="39"/>
-      <c r="T22" s="39"/>
-      <c r="U22" s="39"/>
-      <c r="V22" s="39"/>
-      <c r="W22" s="39"/>
-      <c r="X22" s="39"/>
-      <c r="Y22" s="39"/>
-      <c r="Z22" s="39"/>
-      <c r="AA22" s="39"/>
-    </row>
-    <row r="23" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="29" t="s">
-        <v>23</v>
-      </c>
-      <c r="B23" s="30" t="s">
-        <v>24</v>
-      </c>
-      <c r="C23" s="30"/>
-      <c r="D23" s="30"/>
-      <c r="E23" s="40" t="s">
-        <v>25</v>
-      </c>
-      <c r="F23" s="40"/>
-      <c r="G23" s="40"/>
-      <c r="H23" s="40"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="40"/>
-      <c r="K23" s="27"/>
-      <c r="L23" s="27"/>
-      <c r="M23" s="27"/>
-      <c r="O23" s="8"/>
-      <c r="P23" s="9"/>
-      <c r="Q23" s="39"/>
-      <c r="R23" s="39"/>
-      <c r="S23" s="39"/>
-      <c r="T23" s="39"/>
-      <c r="U23" s="39"/>
-      <c r="V23" s="39"/>
-      <c r="W23" s="39"/>
-      <c r="X23" s="39"/>
-      <c r="Y23" s="39"/>
-      <c r="Z23" s="39"/>
-      <c r="AA23" s="39"/>
-    </row>
-    <row r="24" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="29"/>
-      <c r="B24" s="30"/>
-      <c r="C24" s="30"/>
-      <c r="D24" s="30"/>
-      <c r="E24" s="40"/>
-      <c r="F24" s="40"/>
-      <c r="G24" s="40"/>
-      <c r="H24" s="40"/>
-      <c r="I24" s="40"/>
-      <c r="J24" s="40"/>
-      <c r="K24" s="31" t="s">
-        <v>19</v>
-      </c>
-      <c r="L24" s="31"/>
-      <c r="M24" s="31"/>
-      <c r="O24" s="14" t="n">
-        <v>2017</v>
-      </c>
-      <c r="P24" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q24" s="16" t="s">
-        <v>71</v>
-      </c>
-      <c r="R24" s="16"/>
-      <c r="S24" s="16"/>
-      <c r="T24" s="16"/>
-      <c r="U24" s="16"/>
-      <c r="V24" s="16"/>
-      <c r="W24" s="16"/>
-      <c r="X24" s="16"/>
-      <c r="Y24" s="16"/>
-      <c r="Z24" s="16"/>
-      <c r="AA24" s="16"/>
-    </row>
-    <row r="25" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="29"/>
-      <c r="B25" s="32" t="s">
-        <v>72</v>
-      </c>
-      <c r="C25" s="32"/>
-      <c r="D25" s="32"/>
-      <c r="E25" s="32"/>
-      <c r="F25" s="32"/>
-      <c r="G25" s="32"/>
-      <c r="H25" s="32"/>
-      <c r="I25" s="32"/>
-      <c r="J25" s="32"/>
-      <c r="K25" s="33"/>
-      <c r="L25" s="33"/>
-      <c r="M25" s="33"/>
-      <c r="O25" s="14"/>
-      <c r="P25" s="15"/>
-      <c r="Q25" s="16"/>
-      <c r="R25" s="16"/>
-      <c r="S25" s="16"/>
-      <c r="T25" s="16"/>
-      <c r="U25" s="16"/>
-      <c r="V25" s="16"/>
-      <c r="W25" s="16"/>
-      <c r="X25" s="16"/>
-      <c r="Y25" s="16"/>
-      <c r="Z25" s="16"/>
-      <c r="AA25" s="16"/>
-    </row>
-    <row r="26" customFormat="false" ht="12.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="29"/>
-      <c r="B26" s="32"/>
-      <c r="C26" s="32"/>
-      <c r="D26" s="32"/>
-      <c r="E26" s="32"/>
-      <c r="F26" s="32"/>
-      <c r="G26" s="32"/>
-      <c r="H26" s="32"/>
-      <c r="I26" s="32"/>
-      <c r="J26" s="32"/>
-      <c r="K26" s="33"/>
-      <c r="L26" s="33"/>
-      <c r="M26" s="33"/>
-      <c r="O26" s="14"/>
-      <c r="P26" s="15"/>
-      <c r="Q26" s="16"/>
-      <c r="R26" s="16"/>
-      <c r="S26" s="16"/>
-      <c r="T26" s="16"/>
-      <c r="U26" s="16"/>
-      <c r="V26" s="16"/>
-      <c r="W26" s="16"/>
-      <c r="X26" s="16"/>
-      <c r="Y26" s="16"/>
-      <c r="Z26" s="16"/>
-      <c r="AA26" s="16"/>
-    </row>
-    <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="O27" s="14"/>
-      <c r="P27" s="15"/>
-      <c r="Q27" s="16"/>
-      <c r="R27" s="16"/>
-      <c r="S27" s="16"/>
-      <c r="T27" s="16"/>
-      <c r="U27" s="16"/>
-      <c r="V27" s="16"/>
-      <c r="W27" s="16"/>
-      <c r="X27" s="16"/>
-      <c r="Y27" s="16"/>
-      <c r="Z27" s="16"/>
-      <c r="AA27" s="16"/>
-    </row>
-    <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="42" t="s">
-        <v>2</v>
-      </c>
-      <c r="B28" s="43" t="s">
-        <v>3</v>
-      </c>
-      <c r="C28" s="44" t="s">
-        <v>4</v>
-      </c>
-      <c r="D28" s="44"/>
-      <c r="E28" s="44"/>
-      <c r="F28" s="44"/>
-      <c r="G28" s="44"/>
-      <c r="H28" s="44"/>
-      <c r="I28" s="44"/>
-      <c r="J28" s="44"/>
-      <c r="K28" s="44"/>
-      <c r="L28" s="44"/>
-      <c r="M28" s="44"/>
-      <c r="O28" s="14"/>
-      <c r="P28" s="15"/>
-      <c r="Q28" s="16"/>
-      <c r="R28" s="16"/>
-      <c r="S28" s="16"/>
-      <c r="T28" s="16"/>
-      <c r="U28" s="16"/>
-      <c r="V28" s="16"/>
-      <c r="W28" s="16"/>
-      <c r="X28" s="16"/>
-      <c r="Y28" s="16"/>
-      <c r="Z28" s="16"/>
-      <c r="AA28" s="16"/>
-    </row>
-    <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="42"/>
-      <c r="B29" s="43"/>
-      <c r="C29" s="43"/>
-      <c r="D29" s="44"/>
-      <c r="E29" s="44"/>
-      <c r="F29" s="44"/>
-      <c r="G29" s="44"/>
-      <c r="H29" s="44"/>
-      <c r="I29" s="44"/>
-      <c r="J29" s="44"/>
-      <c r="K29" s="44"/>
-      <c r="L29" s="44"/>
-      <c r="M29" s="44"/>
-      <c r="O29" s="14"/>
-      <c r="P29" s="15"/>
-      <c r="Q29" s="16"/>
-      <c r="R29" s="16"/>
-      <c r="S29" s="16"/>
-      <c r="T29" s="16"/>
-      <c r="U29" s="16"/>
-      <c r="V29" s="16"/>
-      <c r="W29" s="16"/>
-      <c r="X29" s="16"/>
-      <c r="Y29" s="16"/>
-      <c r="Z29" s="16"/>
-      <c r="AA29" s="16"/>
-    </row>
-    <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="45"/>
-      <c r="B30" s="46"/>
-      <c r="C30" s="67" t="s">
-        <v>73</v>
-      </c>
-      <c r="D30" s="67"/>
-      <c r="E30" s="67"/>
-      <c r="F30" s="67"/>
-      <c r="G30" s="67"/>
-      <c r="H30" s="67"/>
-      <c r="I30" s="67"/>
-      <c r="J30" s="67"/>
-      <c r="K30" s="67"/>
-      <c r="L30" s="67"/>
-      <c r="M30" s="67"/>
-      <c r="O30" s="14"/>
-      <c r="P30" s="15"/>
-      <c r="Q30" s="16"/>
-      <c r="R30" s="16"/>
-      <c r="S30" s="16"/>
-      <c r="T30" s="16"/>
-      <c r="U30" s="16"/>
-      <c r="V30" s="16"/>
-      <c r="W30" s="16"/>
-      <c r="X30" s="16"/>
-      <c r="Y30" s="16"/>
-      <c r="Z30" s="16"/>
-      <c r="AA30" s="16"/>
-    </row>
-    <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="45"/>
-      <c r="B31" s="46"/>
-      <c r="C31" s="67"/>
-      <c r="D31" s="67"/>
-      <c r="E31" s="67"/>
-      <c r="F31" s="67"/>
-      <c r="G31" s="67"/>
-      <c r="H31" s="67"/>
-      <c r="I31" s="67"/>
-      <c r="J31" s="67"/>
-      <c r="K31" s="67"/>
-      <c r="L31" s="67"/>
-      <c r="M31" s="67"/>
-      <c r="O31" s="14"/>
-      <c r="P31" s="15"/>
-      <c r="Q31" s="16"/>
-      <c r="R31" s="16"/>
-      <c r="S31" s="16"/>
-      <c r="T31" s="16"/>
-      <c r="U31" s="16"/>
-      <c r="V31" s="16"/>
-      <c r="W31" s="16"/>
-      <c r="X31" s="16"/>
-      <c r="Y31" s="16"/>
-      <c r="Z31" s="16"/>
-      <c r="AA31" s="16"/>
-    </row>
-    <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="48" t="n">
-        <v>2004</v>
-      </c>
-      <c r="B32" s="49" t="n">
-        <v>3</v>
-      </c>
-      <c r="C32" s="41" t="s">
-        <v>74</v>
-      </c>
-      <c r="D32" s="41"/>
-      <c r="E32" s="41"/>
-      <c r="F32" s="41"/>
-      <c r="G32" s="41"/>
-      <c r="H32" s="41"/>
-      <c r="I32" s="41"/>
-      <c r="J32" s="41"/>
-      <c r="K32" s="41"/>
-      <c r="L32" s="41"/>
-      <c r="M32" s="41"/>
-      <c r="O32" s="14"/>
-      <c r="P32" s="15"/>
-      <c r="Q32" s="16"/>
-      <c r="R32" s="16"/>
-      <c r="S32" s="16"/>
-      <c r="T32" s="16"/>
-      <c r="U32" s="16"/>
-      <c r="V32" s="16"/>
-      <c r="W32" s="16"/>
-      <c r="X32" s="16"/>
-      <c r="Y32" s="16"/>
-      <c r="Z32" s="16"/>
-      <c r="AA32" s="16"/>
-    </row>
-    <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="48"/>
-      <c r="B33" s="49"/>
-      <c r="C33" s="41"/>
-      <c r="D33" s="41"/>
-      <c r="E33" s="41"/>
-      <c r="F33" s="41"/>
-      <c r="G33" s="41"/>
-      <c r="H33" s="41"/>
-      <c r="I33" s="41"/>
-      <c r="J33" s="41"/>
-      <c r="K33" s="41"/>
-      <c r="L33" s="41"/>
-      <c r="M33" s="41"/>
-      <c r="O33" s="14"/>
-      <c r="P33" s="15"/>
-      <c r="Q33" s="16"/>
-      <c r="R33" s="16"/>
-      <c r="S33" s="16"/>
-      <c r="T33" s="16"/>
-      <c r="U33" s="16"/>
-      <c r="V33" s="16"/>
-      <c r="W33" s="16"/>
-      <c r="X33" s="16"/>
-      <c r="Y33" s="16"/>
-      <c r="Z33" s="16"/>
-      <c r="AA33" s="16"/>
-    </row>
-    <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="48" t="n">
-        <v>2004</v>
-      </c>
-      <c r="B34" s="49" t="n">
-        <v>4</v>
-      </c>
-      <c r="C34" s="41" t="s">
-        <v>75</v>
-      </c>
-      <c r="D34" s="41"/>
-      <c r="E34" s="41"/>
-      <c r="F34" s="41"/>
-      <c r="G34" s="41"/>
-      <c r="H34" s="41"/>
-      <c r="I34" s="41"/>
-      <c r="J34" s="41"/>
-      <c r="K34" s="41"/>
-      <c r="L34" s="41"/>
-      <c r="M34" s="41"/>
-      <c r="O34" s="14"/>
-      <c r="P34" s="15"/>
-      <c r="Q34" s="16"/>
-      <c r="R34" s="16"/>
-      <c r="S34" s="16"/>
-      <c r="T34" s="16"/>
-      <c r="U34" s="16"/>
-      <c r="V34" s="16"/>
-      <c r="W34" s="16"/>
-      <c r="X34" s="16"/>
-      <c r="Y34" s="16"/>
-      <c r="Z34" s="16"/>
-      <c r="AA34" s="16"/>
-    </row>
-    <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="48"/>
-      <c r="B35" s="49"/>
-      <c r="C35" s="41"/>
-      <c r="D35" s="41"/>
-      <c r="E35" s="41"/>
-      <c r="F35" s="41"/>
-      <c r="G35" s="41"/>
-      <c r="H35" s="41"/>
-      <c r="I35" s="41"/>
-      <c r="J35" s="41"/>
-      <c r="K35" s="41"/>
-      <c r="L35" s="41"/>
-      <c r="M35" s="41"/>
-      <c r="O35" s="14"/>
-      <c r="P35" s="15"/>
-      <c r="Q35" s="16"/>
-      <c r="R35" s="16"/>
-      <c r="S35" s="16"/>
-      <c r="T35" s="16"/>
-      <c r="U35" s="16"/>
-      <c r="V35" s="16"/>
-      <c r="W35" s="16"/>
-      <c r="X35" s="16"/>
-      <c r="Y35" s="16"/>
-      <c r="Z35" s="16"/>
-      <c r="AA35" s="16"/>
-    </row>
-    <row r="36" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A36" s="48" t="n">
-        <v>2006</v>
-      </c>
-      <c r="B36" s="49" t="n">
-        <v>4</v>
-      </c>
-      <c r="C36" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="D36" s="41"/>
-      <c r="E36" s="41"/>
-      <c r="F36" s="41"/>
-      <c r="G36" s="41"/>
-      <c r="H36" s="41"/>
-      <c r="I36" s="41"/>
-      <c r="J36" s="41"/>
-      <c r="K36" s="41"/>
-      <c r="L36" s="41"/>
-      <c r="M36" s="41"/>
-      <c r="O36" s="34"/>
-      <c r="P36" s="35"/>
-      <c r="Q36" s="36"/>
-      <c r="R36" s="36"/>
-      <c r="S36" s="36"/>
-      <c r="T36" s="36"/>
-      <c r="U36" s="36"/>
-      <c r="V36" s="36"/>
-      <c r="W36" s="36"/>
-      <c r="X36" s="36"/>
-      <c r="Y36" s="36"/>
-      <c r="Z36" s="36"/>
-      <c r="AA36" s="36"/>
-    </row>
-    <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A37" s="48"/>
-      <c r="B37" s="49"/>
-      <c r="C37" s="41"/>
-      <c r="D37" s="41"/>
-      <c r="E37" s="41"/>
-      <c r="F37" s="41"/>
-      <c r="G37" s="41"/>
-      <c r="H37" s="41"/>
-      <c r="I37" s="41"/>
-      <c r="J37" s="41"/>
-      <c r="K37" s="41"/>
-      <c r="L37" s="41"/>
-      <c r="M37" s="41"/>
-      <c r="O37" s="34"/>
-      <c r="P37" s="35"/>
-      <c r="Q37" s="36"/>
-      <c r="R37" s="36"/>
-      <c r="S37" s="36"/>
-      <c r="T37" s="36"/>
-      <c r="U37" s="36"/>
-      <c r="V37" s="36"/>
-      <c r="W37" s="36"/>
-      <c r="X37" s="36"/>
-      <c r="Y37" s="36"/>
-      <c r="Z37" s="36"/>
-      <c r="AA37" s="36"/>
-    </row>
-    <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A38" s="48" t="n">
-        <v>2008</v>
-      </c>
-      <c r="B38" s="49" t="n">
-        <v>3</v>
-      </c>
-      <c r="C38" s="41" t="s">
-        <v>77</v>
-      </c>
-      <c r="D38" s="41"/>
-      <c r="E38" s="41"/>
-      <c r="F38" s="41"/>
-      <c r="G38" s="41"/>
-      <c r="H38" s="41"/>
-      <c r="I38" s="41"/>
-      <c r="J38" s="41"/>
-      <c r="K38" s="41"/>
-      <c r="L38" s="41"/>
-      <c r="M38" s="41"/>
-      <c r="O38" s="7"/>
-      <c r="P38" s="7"/>
-      <c r="Q38" s="7"/>
-      <c r="R38" s="7"/>
-      <c r="S38" s="7"/>
-      <c r="T38" s="7"/>
-      <c r="U38" s="7"/>
-      <c r="V38" s="7"/>
-      <c r="W38" s="7"/>
-      <c r="X38" s="7"/>
-      <c r="Y38" s="7"/>
-      <c r="Z38" s="7"/>
-      <c r="AA38" s="7"/>
-    </row>
-    <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A39" s="48"/>
-      <c r="B39" s="49"/>
-      <c r="C39" s="41"/>
-      <c r="D39" s="41"/>
-      <c r="E39" s="41"/>
-      <c r="F39" s="41"/>
-      <c r="G39" s="41"/>
-      <c r="H39" s="41"/>
-      <c r="I39" s="41"/>
-      <c r="J39" s="41"/>
-      <c r="K39" s="41"/>
-      <c r="L39" s="41"/>
-      <c r="M39" s="41"/>
-      <c r="O39" s="50" t="s">
-        <v>36</v>
-      </c>
-      <c r="P39" s="50"/>
-      <c r="Q39" s="50"/>
-      <c r="R39" s="50"/>
-      <c r="S39" s="50"/>
-      <c r="T39" s="50"/>
-      <c r="U39" s="50"/>
-      <c r="V39" s="50"/>
-      <c r="W39" s="50"/>
-      <c r="X39" s="50" t="s">
-        <v>37</v>
-      </c>
-      <c r="Y39" s="50"/>
-      <c r="Z39" s="50"/>
-      <c r="AA39" s="50"/>
-    </row>
-    <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A40" s="48"/>
-      <c r="B40" s="49"/>
-      <c r="C40" s="41"/>
-      <c r="D40" s="41"/>
-      <c r="E40" s="41"/>
-      <c r="F40" s="41"/>
-      <c r="G40" s="41"/>
-      <c r="H40" s="41"/>
-      <c r="I40" s="41"/>
-      <c r="J40" s="41"/>
-      <c r="K40" s="41"/>
-      <c r="L40" s="41"/>
-      <c r="M40" s="41"/>
-      <c r="O40" s="68" t="s">
-        <v>78</v>
-      </c>
-      <c r="P40" s="68"/>
-      <c r="Q40" s="68"/>
-      <c r="R40" s="68"/>
-      <c r="S40" s="68"/>
-      <c r="T40" s="68"/>
-      <c r="U40" s="68"/>
-      <c r="V40" s="68"/>
-      <c r="W40" s="68"/>
-      <c r="X40" s="52" t="s">
-        <v>79</v>
-      </c>
-      <c r="Y40" s="52"/>
-      <c r="Z40" s="52"/>
-      <c r="AA40" s="52"/>
-    </row>
-    <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="48"/>
-      <c r="B41" s="49"/>
-      <c r="C41" s="41"/>
-      <c r="D41" s="41"/>
-      <c r="E41" s="41"/>
-      <c r="F41" s="41"/>
-      <c r="G41" s="41"/>
-      <c r="H41" s="41"/>
-      <c r="I41" s="41"/>
-      <c r="J41" s="41"/>
-      <c r="K41" s="41"/>
-      <c r="L41" s="41"/>
-      <c r="M41" s="41"/>
-      <c r="O41" s="68"/>
-      <c r="P41" s="68"/>
-      <c r="Q41" s="68"/>
-      <c r="R41" s="68"/>
-      <c r="S41" s="68"/>
-      <c r="T41" s="68"/>
-      <c r="U41" s="68"/>
-      <c r="V41" s="68"/>
-      <c r="W41" s="68"/>
-      <c r="X41" s="52"/>
-      <c r="Y41" s="52"/>
-      <c r="Z41" s="52"/>
-      <c r="AA41" s="52"/>
-    </row>
-    <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A42" s="48"/>
-      <c r="B42" s="49"/>
-      <c r="C42" s="41" t="s">
-        <v>80</v>
-      </c>
-      <c r="D42" s="41"/>
-      <c r="E42" s="41"/>
-      <c r="F42" s="41"/>
-      <c r="G42" s="41"/>
-      <c r="H42" s="41"/>
-      <c r="I42" s="41"/>
-      <c r="J42" s="41"/>
-      <c r="K42" s="41"/>
-      <c r="L42" s="41"/>
-      <c r="M42" s="41"/>
-      <c r="O42" s="68"/>
-      <c r="P42" s="68"/>
-      <c r="Q42" s="68"/>
-      <c r="R42" s="68"/>
-      <c r="S42" s="68"/>
-      <c r="T42" s="68"/>
-      <c r="U42" s="68"/>
-      <c r="V42" s="68"/>
-      <c r="W42" s="68"/>
-      <c r="X42" s="50" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y42" s="50"/>
-      <c r="Z42" s="50"/>
-      <c r="AA42" s="50"/>
-    </row>
-    <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A43" s="48"/>
-      <c r="B43" s="49"/>
-      <c r="C43" s="41"/>
-      <c r="D43" s="41"/>
-      <c r="E43" s="41"/>
-      <c r="F43" s="41"/>
-      <c r="G43" s="41"/>
-      <c r="H43" s="41"/>
-      <c r="I43" s="41"/>
-      <c r="J43" s="41"/>
-      <c r="K43" s="41"/>
-      <c r="L43" s="41"/>
-      <c r="M43" s="41"/>
-      <c r="O43" s="68"/>
-      <c r="P43" s="68"/>
-      <c r="Q43" s="68"/>
-      <c r="R43" s="68"/>
-      <c r="S43" s="68"/>
-      <c r="T43" s="68"/>
-      <c r="U43" s="68"/>
-      <c r="V43" s="68"/>
-      <c r="W43" s="68"/>
-      <c r="X43" s="52" t="s">
-        <v>81</v>
-      </c>
-      <c r="Y43" s="52"/>
-      <c r="Z43" s="52"/>
-      <c r="AA43" s="52"/>
-    </row>
-    <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A44" s="48" t="n">
-        <v>2007</v>
-      </c>
-      <c r="B44" s="49" t="n">
-        <v>4</v>
-      </c>
-      <c r="C44" s="41" t="s">
-        <v>82</v>
-      </c>
-      <c r="D44" s="41"/>
-      <c r="E44" s="41"/>
-      <c r="F44" s="41"/>
-      <c r="G44" s="41"/>
-      <c r="H44" s="41"/>
-      <c r="I44" s="41"/>
-      <c r="J44" s="41"/>
-      <c r="K44" s="41"/>
-      <c r="L44" s="41"/>
-      <c r="M44" s="41"/>
-      <c r="O44" s="68"/>
-      <c r="P44" s="68"/>
-      <c r="Q44" s="68"/>
-      <c r="R44" s="68"/>
-      <c r="S44" s="68"/>
-      <c r="T44" s="68"/>
-      <c r="U44" s="68"/>
-      <c r="V44" s="68"/>
-      <c r="W44" s="68"/>
-      <c r="X44" s="52"/>
-      <c r="Y44" s="52"/>
-      <c r="Z44" s="52"/>
-      <c r="AA44" s="52"/>
-    </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A45" s="48"/>
-      <c r="B45" s="49"/>
-      <c r="C45" s="41"/>
-      <c r="D45" s="41"/>
-      <c r="E45" s="41"/>
-      <c r="F45" s="41"/>
-      <c r="G45" s="41"/>
-      <c r="H45" s="41"/>
-      <c r="I45" s="41"/>
-      <c r="J45" s="41"/>
-      <c r="K45" s="41"/>
-      <c r="L45" s="41"/>
-      <c r="M45" s="41"/>
-      <c r="O45" s="68"/>
-      <c r="P45" s="68"/>
-      <c r="Q45" s="68"/>
-      <c r="R45" s="68"/>
-      <c r="S45" s="68"/>
-      <c r="T45" s="68"/>
-      <c r="U45" s="68"/>
-      <c r="V45" s="68"/>
-      <c r="W45" s="68"/>
-      <c r="X45" s="50" t="s">
-        <v>45</v>
-      </c>
-      <c r="Y45" s="50"/>
-      <c r="Z45" s="50" t="s">
-        <v>46</v>
-      </c>
-      <c r="AA45" s="50"/>
-    </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A46" s="48" t="n">
-        <v>2008</v>
-      </c>
-      <c r="B46" s="49" t="n">
-        <v>4</v>
-      </c>
-      <c r="C46" s="41" t="s">
-        <v>83</v>
-      </c>
-      <c r="D46" s="41"/>
-      <c r="E46" s="41"/>
-      <c r="F46" s="41"/>
-      <c r="G46" s="41"/>
-      <c r="H46" s="41"/>
-      <c r="I46" s="41"/>
-      <c r="J46" s="41"/>
-      <c r="K46" s="41"/>
-      <c r="L46" s="41"/>
-      <c r="M46" s="41"/>
-      <c r="O46" s="68"/>
-      <c r="P46" s="68"/>
-      <c r="Q46" s="68"/>
-      <c r="R46" s="68"/>
-      <c r="S46" s="68"/>
-      <c r="T46" s="68"/>
-      <c r="U46" s="68"/>
-      <c r="V46" s="68"/>
-      <c r="W46" s="68"/>
-      <c r="X46" s="53" t="s">
-        <v>48</v>
-      </c>
-      <c r="Y46" s="53"/>
-      <c r="Z46" s="54" t="s">
-        <v>48</v>
-      </c>
-      <c r="AA46" s="54"/>
-    </row>
-    <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A47" s="48"/>
-      <c r="B47" s="49"/>
-      <c r="C47" s="41"/>
-      <c r="D47" s="41"/>
-      <c r="E47" s="41"/>
-      <c r="F47" s="41"/>
-      <c r="G47" s="41"/>
-      <c r="H47" s="41"/>
-      <c r="I47" s="41"/>
-      <c r="J47" s="41"/>
-      <c r="K47" s="41"/>
-      <c r="L47" s="41"/>
-      <c r="M47" s="41"/>
-      <c r="O47" s="68"/>
-      <c r="P47" s="68"/>
-      <c r="Q47" s="68"/>
-      <c r="R47" s="68"/>
-      <c r="S47" s="68"/>
-      <c r="T47" s="68"/>
-      <c r="U47" s="68"/>
-      <c r="V47" s="68"/>
-      <c r="W47" s="68"/>
-      <c r="X47" s="53"/>
-      <c r="Y47" s="53"/>
-      <c r="Z47" s="54"/>
-      <c r="AA47" s="54"/>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="48"/>
-      <c r="B48" s="49"/>
-      <c r="C48" s="41" t="s">
-        <v>84</v>
-      </c>
-      <c r="D48" s="41"/>
-      <c r="E48" s="41"/>
-      <c r="F48" s="41"/>
-      <c r="G48" s="41"/>
-      <c r="H48" s="41"/>
-      <c r="I48" s="41"/>
-      <c r="J48" s="41"/>
-      <c r="K48" s="41"/>
-      <c r="L48" s="41"/>
-      <c r="M48" s="41"/>
-      <c r="O48" s="7"/>
-      <c r="P48" s="7"/>
-      <c r="Q48" s="7"/>
-      <c r="R48" s="7"/>
-      <c r="S48" s="7"/>
-      <c r="T48" s="7"/>
-      <c r="U48" s="7"/>
-      <c r="V48" s="7"/>
-      <c r="W48" s="7"/>
-      <c r="X48" s="55"/>
-      <c r="Y48" s="55"/>
-      <c r="Z48" s="55"/>
-      <c r="AA48" s="55"/>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="48"/>
-      <c r="B49" s="49"/>
-      <c r="C49" s="41"/>
-      <c r="D49" s="41"/>
-      <c r="E49" s="41"/>
-      <c r="F49" s="41"/>
-      <c r="G49" s="41"/>
-      <c r="H49" s="41"/>
-      <c r="I49" s="41"/>
-      <c r="J49" s="41"/>
-      <c r="K49" s="41"/>
-      <c r="L49" s="41"/>
-      <c r="M49" s="41"/>
-      <c r="O49" s="56" t="s">
-        <v>50</v>
-      </c>
-      <c r="P49" s="56"/>
-      <c r="Q49" s="56"/>
-      <c r="R49" s="56"/>
-      <c r="S49" s="56"/>
-      <c r="T49" s="56"/>
-      <c r="U49" s="56"/>
-      <c r="V49" s="56"/>
-      <c r="W49" s="56"/>
-      <c r="X49" s="56"/>
-      <c r="Y49" s="56"/>
-      <c r="Z49" s="56"/>
-      <c r="AA49" s="56"/>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="48" t="n">
-        <v>2010</v>
-      </c>
-      <c r="B50" s="49" t="n">
-        <v>7</v>
-      </c>
-      <c r="C50" s="41" t="s">
-        <v>85</v>
-      </c>
-      <c r="D50" s="41"/>
-      <c r="E50" s="41"/>
-      <c r="F50" s="41"/>
-      <c r="G50" s="41"/>
-      <c r="H50" s="41"/>
-      <c r="I50" s="41"/>
-      <c r="J50" s="41"/>
-      <c r="K50" s="41"/>
-      <c r="L50" s="41"/>
-      <c r="M50" s="41"/>
-      <c r="O50" s="56"/>
-      <c r="P50" s="56"/>
-      <c r="Q50" s="56"/>
-      <c r="R50" s="56"/>
-      <c r="S50" s="56"/>
-      <c r="T50" s="56"/>
-      <c r="U50" s="56"/>
-      <c r="V50" s="56"/>
-      <c r="W50" s="56"/>
-      <c r="X50" s="56"/>
-      <c r="Y50" s="56"/>
-      <c r="Z50" s="56"/>
-      <c r="AA50" s="56"/>
-    </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="48"/>
-      <c r="B51" s="49"/>
-      <c r="C51" s="41"/>
-      <c r="D51" s="41"/>
-      <c r="E51" s="41"/>
-      <c r="F51" s="41"/>
-      <c r="G51" s="41"/>
-      <c r="H51" s="41"/>
-      <c r="I51" s="41"/>
-      <c r="J51" s="41"/>
-      <c r="K51" s="41"/>
-      <c r="L51" s="41"/>
-      <c r="M51" s="41"/>
-      <c r="O51" s="57" t="s">
-        <v>86</v>
-      </c>
-      <c r="P51" s="57"/>
-      <c r="Q51" s="57"/>
-      <c r="R51" s="57"/>
-      <c r="S51" s="57"/>
-      <c r="T51" s="57"/>
-      <c r="U51" s="57"/>
-      <c r="V51" s="57"/>
-      <c r="W51" s="57"/>
-      <c r="X51" s="57"/>
-      <c r="Y51" s="57"/>
-      <c r="Z51" s="57"/>
-      <c r="AA51" s="57"/>
-    </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="48" t="n">
-        <v>2011</v>
-      </c>
-      <c r="B52" s="49" t="n">
-        <v>8</v>
-      </c>
-      <c r="C52" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="D52" s="41"/>
-      <c r="E52" s="41"/>
-      <c r="F52" s="41"/>
-      <c r="G52" s="41"/>
-      <c r="H52" s="41"/>
-      <c r="I52" s="41"/>
-      <c r="J52" s="41"/>
-      <c r="K52" s="41"/>
-      <c r="L52" s="41"/>
-      <c r="M52" s="41"/>
-      <c r="O52" s="57"/>
-      <c r="P52" s="57"/>
-      <c r="Q52" s="57"/>
-      <c r="R52" s="57"/>
-      <c r="S52" s="57"/>
-      <c r="T52" s="57"/>
-      <c r="U52" s="57"/>
-      <c r="V52" s="57"/>
-      <c r="W52" s="57"/>
-      <c r="X52" s="57"/>
-      <c r="Y52" s="57"/>
-      <c r="Z52" s="57"/>
-      <c r="AA52" s="57"/>
-    </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="48"/>
-      <c r="B53" s="49"/>
-      <c r="C53" s="41"/>
-      <c r="D53" s="41"/>
-      <c r="E53" s="41"/>
-      <c r="F53" s="41"/>
-      <c r="G53" s="41"/>
-      <c r="H53" s="41"/>
-      <c r="I53" s="41"/>
-      <c r="J53" s="41"/>
-      <c r="K53" s="41"/>
-      <c r="L53" s="41"/>
-      <c r="M53" s="41"/>
-      <c r="O53" s="57"/>
-      <c r="P53" s="57"/>
-      <c r="Q53" s="57"/>
-      <c r="R53" s="57"/>
-      <c r="S53" s="57"/>
-      <c r="T53" s="57"/>
-      <c r="U53" s="57"/>
-      <c r="V53" s="57"/>
-      <c r="W53" s="57"/>
-      <c r="X53" s="57"/>
-      <c r="Y53" s="57"/>
-      <c r="Z53" s="57"/>
-      <c r="AA53" s="57"/>
-    </row>
-    <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A54" s="48" t="n">
-        <v>2011</v>
-      </c>
-      <c r="B54" s="49" t="n">
-        <v>9</v>
-      </c>
-      <c r="C54" s="41" t="s">
-        <v>88</v>
-      </c>
-      <c r="D54" s="41"/>
-      <c r="E54" s="41"/>
-      <c r="F54" s="41"/>
-      <c r="G54" s="41"/>
-      <c r="H54" s="41"/>
-      <c r="I54" s="41"/>
-      <c r="J54" s="41"/>
-      <c r="K54" s="41"/>
-      <c r="L54" s="41"/>
-      <c r="M54" s="41"/>
-      <c r="O54" s="57"/>
-      <c r="P54" s="57"/>
-      <c r="Q54" s="57"/>
-      <c r="R54" s="57"/>
-      <c r="S54" s="57"/>
-      <c r="T54" s="57"/>
-      <c r="U54" s="57"/>
-      <c r="V54" s="57"/>
-      <c r="W54" s="57"/>
-      <c r="X54" s="57"/>
-      <c r="Y54" s="57"/>
-      <c r="Z54" s="57"/>
-      <c r="AA54" s="57"/>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A55" s="48"/>
-      <c r="B55" s="49"/>
-      <c r="C55" s="41"/>
-      <c r="D55" s="41"/>
-      <c r="E55" s="41"/>
-      <c r="F55" s="41"/>
-      <c r="G55" s="41"/>
-      <c r="H55" s="41"/>
-      <c r="I55" s="41"/>
-      <c r="J55" s="41"/>
-      <c r="K55" s="41"/>
-      <c r="L55" s="41"/>
-      <c r="M55" s="41"/>
-      <c r="O55" s="57"/>
-      <c r="P55" s="57"/>
-      <c r="Q55" s="57"/>
-      <c r="R55" s="57"/>
-      <c r="S55" s="57"/>
-      <c r="T55" s="57"/>
-      <c r="U55" s="57"/>
-      <c r="V55" s="57"/>
-      <c r="W55" s="57"/>
-      <c r="X55" s="57"/>
-      <c r="Y55" s="57"/>
-      <c r="Z55" s="57"/>
-      <c r="AA55" s="57"/>
-    </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A56" s="48"/>
-      <c r="B56" s="49"/>
-      <c r="C56" s="41" t="s">
-        <v>89</v>
-      </c>
-      <c r="D56" s="41"/>
-      <c r="E56" s="41"/>
-      <c r="F56" s="41"/>
-      <c r="G56" s="41"/>
-      <c r="H56" s="41"/>
-      <c r="I56" s="41"/>
-      <c r="J56" s="41"/>
-      <c r="K56" s="41"/>
-      <c r="L56" s="41"/>
-      <c r="M56" s="41"/>
-      <c r="O56" s="57"/>
-      <c r="P56" s="57"/>
-      <c r="Q56" s="57"/>
-      <c r="R56" s="57"/>
-      <c r="S56" s="57"/>
-      <c r="T56" s="57"/>
-      <c r="U56" s="57"/>
-      <c r="V56" s="57"/>
-      <c r="W56" s="57"/>
-      <c r="X56" s="57"/>
-      <c r="Y56" s="57"/>
-      <c r="Z56" s="57"/>
-      <c r="AA56" s="57"/>
-    </row>
-    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A57" s="48"/>
-      <c r="B57" s="49"/>
-      <c r="C57" s="41"/>
-      <c r="D57" s="41"/>
-      <c r="E57" s="41"/>
-      <c r="F57" s="41"/>
-      <c r="G57" s="41"/>
-      <c r="H57" s="41"/>
-      <c r="I57" s="41"/>
-      <c r="J57" s="41"/>
-      <c r="K57" s="41"/>
-      <c r="L57" s="41"/>
-      <c r="M57" s="41"/>
-      <c r="O57" s="57"/>
-      <c r="P57" s="57"/>
-      <c r="Q57" s="57"/>
-      <c r="R57" s="57"/>
-      <c r="S57" s="57"/>
-      <c r="T57" s="57"/>
-      <c r="U57" s="57"/>
-      <c r="V57" s="57"/>
-      <c r="W57" s="57"/>
-      <c r="X57" s="57"/>
-      <c r="Y57" s="57"/>
-      <c r="Z57" s="57"/>
-      <c r="AA57" s="57"/>
-    </row>
-    <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A58" s="48" t="n">
-        <v>2016</v>
-      </c>
-      <c r="B58" s="49" t="n">
-        <v>4</v>
-      </c>
-      <c r="C58" s="41" t="s">
-        <v>87</v>
-      </c>
-      <c r="D58" s="41"/>
-      <c r="E58" s="41"/>
-      <c r="F58" s="41"/>
-      <c r="G58" s="41"/>
-      <c r="H58" s="41"/>
-      <c r="I58" s="41"/>
-      <c r="J58" s="41"/>
-      <c r="K58" s="41"/>
-      <c r="L58" s="41"/>
-      <c r="M58" s="41"/>
-      <c r="O58" s="57"/>
-      <c r="P58" s="57"/>
-      <c r="Q58" s="57"/>
-      <c r="R58" s="57"/>
-      <c r="S58" s="57"/>
-      <c r="T58" s="57"/>
-      <c r="U58" s="57"/>
-      <c r="V58" s="57"/>
-      <c r="W58" s="57"/>
-      <c r="X58" s="57"/>
-      <c r="Y58" s="57"/>
-      <c r="Z58" s="57"/>
-      <c r="AA58" s="57"/>
-    </row>
-    <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A59" s="48"/>
-      <c r="B59" s="49"/>
-      <c r="C59" s="41"/>
-      <c r="D59" s="41"/>
-      <c r="E59" s="41"/>
-      <c r="F59" s="41"/>
-      <c r="G59" s="41"/>
-      <c r="H59" s="41"/>
-      <c r="I59" s="41"/>
-      <c r="J59" s="41"/>
-      <c r="K59" s="41"/>
-      <c r="L59" s="41"/>
-      <c r="M59" s="41"/>
-      <c r="O59" s="57"/>
-      <c r="P59" s="57"/>
-      <c r="Q59" s="57"/>
-      <c r="R59" s="57"/>
-      <c r="S59" s="57"/>
-      <c r="T59" s="57"/>
-      <c r="U59" s="57"/>
-      <c r="V59" s="57"/>
-      <c r="W59" s="57"/>
-      <c r="X59" s="57"/>
-      <c r="Y59" s="57"/>
-      <c r="Z59" s="57"/>
-      <c r="AA59" s="57"/>
-    </row>
-    <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="59" t="n">
-        <v>2016</v>
-      </c>
-      <c r="B60" s="60" t="n">
-        <v>7</v>
-      </c>
-      <c r="C60" s="61" t="s">
-        <v>90</v>
-      </c>
-      <c r="D60" s="61"/>
-      <c r="E60" s="61"/>
-      <c r="F60" s="61"/>
-      <c r="G60" s="61"/>
-      <c r="H60" s="61"/>
-      <c r="I60" s="61"/>
-      <c r="J60" s="61"/>
-      <c r="K60" s="61"/>
-      <c r="L60" s="61"/>
-      <c r="M60" s="61"/>
-      <c r="O60" s="57"/>
-      <c r="P60" s="57"/>
-      <c r="Q60" s="57"/>
-      <c r="R60" s="57"/>
-      <c r="S60" s="57"/>
-      <c r="T60" s="57"/>
-      <c r="U60" s="57"/>
-      <c r="V60" s="57"/>
-      <c r="W60" s="57"/>
-      <c r="X60" s="57"/>
-      <c r="Y60" s="57"/>
-      <c r="Z60" s="57"/>
-      <c r="AA60" s="57"/>
-    </row>
-    <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="59"/>
-      <c r="B61" s="60"/>
-      <c r="C61" s="61"/>
-      <c r="D61" s="61"/>
-      <c r="E61" s="61"/>
-      <c r="F61" s="61"/>
-      <c r="G61" s="61"/>
-      <c r="H61" s="61"/>
-      <c r="I61" s="61"/>
-      <c r="J61" s="61"/>
-      <c r="K61" s="61"/>
-      <c r="L61" s="61"/>
-      <c r="M61" s="61"/>
-      <c r="O61" s="57"/>
-      <c r="P61" s="57"/>
-      <c r="Q61" s="57"/>
-      <c r="R61" s="57"/>
-      <c r="S61" s="57"/>
-      <c r="T61" s="57"/>
-      <c r="U61" s="57"/>
-      <c r="V61" s="57"/>
-      <c r="W61" s="57"/>
-      <c r="X61" s="57"/>
-      <c r="Y61" s="57"/>
-      <c r="Z61" s="57"/>
-      <c r="AA61" s="57"/>
-    </row>
-    <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="62" t="s">
-        <v>55</v>
-      </c>
-      <c r="B62" s="63" t="s">
-        <v>56</v>
-      </c>
-      <c r="C62" s="63"/>
-      <c r="D62" s="63"/>
-      <c r="E62" s="63"/>
-      <c r="F62" s="63"/>
-      <c r="G62" s="63"/>
-      <c r="H62" s="63"/>
-      <c r="I62" s="63"/>
-      <c r="J62" s="63"/>
-      <c r="K62" s="63"/>
-      <c r="L62" s="63"/>
-      <c r="M62" s="63"/>
-      <c r="O62" s="64"/>
-      <c r="P62" s="64"/>
-      <c r="Q62" s="64"/>
-      <c r="R62" s="64"/>
-      <c r="S62" s="64"/>
-      <c r="T62" s="64"/>
-      <c r="U62" s="64"/>
-      <c r="V62" s="64"/>
-      <c r="W62" s="64"/>
-      <c r="X62" s="64"/>
-      <c r="Y62" s="64"/>
-      <c r="Z62" s="64"/>
-      <c r="AA62" s="64"/>
-    </row>
-    <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="62"/>
-      <c r="B63" s="63"/>
-      <c r="C63" s="63"/>
-      <c r="D63" s="63"/>
-      <c r="E63" s="63"/>
-      <c r="F63" s="63"/>
-      <c r="G63" s="63"/>
-      <c r="H63" s="63"/>
-      <c r="I63" s="63"/>
-      <c r="J63" s="63"/>
-      <c r="K63" s="63"/>
-      <c r="L63" s="63"/>
-      <c r="M63" s="63"/>
-      <c r="O63" s="65"/>
-      <c r="P63" s="65"/>
-      <c r="Q63" s="65"/>
-      <c r="R63" s="65"/>
-      <c r="S63" s="65"/>
-      <c r="T63" s="65"/>
-      <c r="U63" s="65"/>
-      <c r="V63" s="65"/>
-      <c r="W63" s="65"/>
-      <c r="X63" s="65"/>
-      <c r="Y63" s="65"/>
-      <c r="Z63" s="65"/>
-      <c r="AA63" s="65"/>
-    </row>
-    <row r="64" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O64" s="65"/>
-      <c r="P64" s="65"/>
-      <c r="Q64" s="65"/>
-      <c r="R64" s="65"/>
-      <c r="S64" s="65"/>
-      <c r="T64" s="65"/>
-      <c r="U64" s="65"/>
-      <c r="V64" s="65"/>
-      <c r="W64" s="65"/>
-      <c r="X64" s="65"/>
-      <c r="Y64" s="65"/>
-      <c r="Z64" s="65"/>
-      <c r="AA64" s="65"/>
-    </row>
-    <row r="65" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O65" s="65"/>
-      <c r="P65" s="65"/>
-      <c r="Q65" s="65"/>
-      <c r="R65" s="65"/>
-      <c r="S65" s="65"/>
-      <c r="T65" s="65"/>
-      <c r="U65" s="65"/>
-      <c r="V65" s="65"/>
-      <c r="W65" s="65"/>
-      <c r="X65" s="65"/>
-      <c r="Y65" s="65"/>
-      <c r="Z65" s="65"/>
-      <c r="AA65" s="65"/>
-    </row>
-  </sheetData>
-  <mergeCells count="150">
-    <mergeCell ref="A1:C1"/>
-    <mergeCell ref="E1:J1"/>
-    <mergeCell ref="Q1:AA1"/>
-    <mergeCell ref="A2:C3"/>
-    <mergeCell ref="E3:J4"/>
-    <mergeCell ref="O3:O4"/>
-    <mergeCell ref="P3:P4"/>
-    <mergeCell ref="Q3:AA4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="B5:J6"/>
-    <mergeCell ref="O5:O6"/>
-    <mergeCell ref="P5:P6"/>
-    <mergeCell ref="Q5:AA6"/>
-    <mergeCell ref="A7:A12"/>
-    <mergeCell ref="B7:J12"/>
-    <mergeCell ref="O7:O8"/>
-    <mergeCell ref="P7:P8"/>
-    <mergeCell ref="Q7:AA8"/>
-    <mergeCell ref="O9:O10"/>
-    <mergeCell ref="P9:P10"/>
-    <mergeCell ref="Q9:AA10"/>
-    <mergeCell ref="O11:O12"/>
-    <mergeCell ref="P11:P12"/>
-    <mergeCell ref="Q11:AA12"/>
-    <mergeCell ref="A13:A14"/>
-    <mergeCell ref="B13:D14"/>
-    <mergeCell ref="E13:F14"/>
-    <mergeCell ref="G13:J14"/>
-    <mergeCell ref="K13:K14"/>
-    <mergeCell ref="L13:M14"/>
-    <mergeCell ref="O13:O14"/>
-    <mergeCell ref="P13:P14"/>
-    <mergeCell ref="Q13:AA14"/>
-    <mergeCell ref="A15:A16"/>
-    <mergeCell ref="B15:J16"/>
-    <mergeCell ref="K15:M15"/>
-    <mergeCell ref="O15:O16"/>
-    <mergeCell ref="P15:P16"/>
-    <mergeCell ref="Q15:AA16"/>
-    <mergeCell ref="K16:M17"/>
-    <mergeCell ref="A17:A20"/>
-    <mergeCell ref="B17:J18"/>
-    <mergeCell ref="O17:O18"/>
-    <mergeCell ref="P17:P18"/>
-    <mergeCell ref="Q17:AA18"/>
-    <mergeCell ref="K18:M18"/>
-    <mergeCell ref="B19:J20"/>
-    <mergeCell ref="K19:M20"/>
-    <mergeCell ref="O19:O20"/>
-    <mergeCell ref="P19:P20"/>
-    <mergeCell ref="Q19:AA20"/>
-    <mergeCell ref="A21:A22"/>
-    <mergeCell ref="B21:J22"/>
-    <mergeCell ref="K21:M21"/>
-    <mergeCell ref="K22:M23"/>
-    <mergeCell ref="O22:O23"/>
-    <mergeCell ref="P22:P23"/>
-    <mergeCell ref="Q22:AA23"/>
-    <mergeCell ref="A23:A26"/>
-    <mergeCell ref="B23:D24"/>
-    <mergeCell ref="E23:J24"/>
-    <mergeCell ref="K24:M24"/>
-    <mergeCell ref="O24:O25"/>
-    <mergeCell ref="P24:P25"/>
-    <mergeCell ref="Q24:AA25"/>
-    <mergeCell ref="B25:J26"/>
-    <mergeCell ref="K25:M26"/>
-    <mergeCell ref="O26:O27"/>
-    <mergeCell ref="P26:P27"/>
-    <mergeCell ref="Q26:AA27"/>
-    <mergeCell ref="A28:A29"/>
-    <mergeCell ref="B28:B29"/>
-    <mergeCell ref="C28:M29"/>
-    <mergeCell ref="O28:O29"/>
-    <mergeCell ref="P28:P29"/>
-    <mergeCell ref="Q28:AA29"/>
-    <mergeCell ref="A30:A31"/>
-    <mergeCell ref="B30:B31"/>
-    <mergeCell ref="C30:M31"/>
-    <mergeCell ref="O30:O31"/>
-    <mergeCell ref="P30:P31"/>
-    <mergeCell ref="Q30:AA31"/>
-    <mergeCell ref="A32:A33"/>
-    <mergeCell ref="B32:B33"/>
-    <mergeCell ref="C32:M33"/>
-    <mergeCell ref="O32:O33"/>
-    <mergeCell ref="P32:P33"/>
-    <mergeCell ref="Q32:AA33"/>
-    <mergeCell ref="A34:A35"/>
-    <mergeCell ref="B34:B35"/>
-    <mergeCell ref="C34:M35"/>
-    <mergeCell ref="O34:O35"/>
-    <mergeCell ref="P34:P35"/>
-    <mergeCell ref="Q34:AA35"/>
-    <mergeCell ref="A36:A37"/>
-    <mergeCell ref="B36:B37"/>
-    <mergeCell ref="C36:M37"/>
-    <mergeCell ref="O36:O37"/>
-    <mergeCell ref="P36:P37"/>
-    <mergeCell ref="Q36:AA37"/>
-    <mergeCell ref="A38:A39"/>
-    <mergeCell ref="B38:B39"/>
-    <mergeCell ref="C38:M39"/>
-    <mergeCell ref="O39:W39"/>
-    <mergeCell ref="X39:AA39"/>
-    <mergeCell ref="A40:A41"/>
-    <mergeCell ref="B40:B41"/>
-    <mergeCell ref="C40:M41"/>
-    <mergeCell ref="O40:W47"/>
-    <mergeCell ref="X40:AA41"/>
-    <mergeCell ref="A42:A43"/>
-    <mergeCell ref="B42:B43"/>
-    <mergeCell ref="C42:M43"/>
-    <mergeCell ref="X42:AA42"/>
-    <mergeCell ref="X43:AA44"/>
-    <mergeCell ref="A44:A45"/>
-    <mergeCell ref="B44:B45"/>
-    <mergeCell ref="C44:M45"/>
-    <mergeCell ref="X45:Y45"/>
-    <mergeCell ref="Z45:AA45"/>
-    <mergeCell ref="A46:A47"/>
-    <mergeCell ref="B46:B47"/>
-    <mergeCell ref="C46:M47"/>
-    <mergeCell ref="X46:Y47"/>
-    <mergeCell ref="Z46:AA47"/>
-    <mergeCell ref="A48:A49"/>
-    <mergeCell ref="B48:B49"/>
-    <mergeCell ref="C48:M49"/>
-    <mergeCell ref="O49:AA50"/>
-    <mergeCell ref="A50:A51"/>
-    <mergeCell ref="B50:B51"/>
-    <mergeCell ref="C50:M51"/>
-    <mergeCell ref="O51:AA61"/>
-    <mergeCell ref="A52:A53"/>
-    <mergeCell ref="B52:B53"/>
-    <mergeCell ref="C52:M53"/>
-    <mergeCell ref="A54:A55"/>
-    <mergeCell ref="B54:B55"/>
-    <mergeCell ref="C54:M55"/>
-    <mergeCell ref="A56:A57"/>
-    <mergeCell ref="B56:B57"/>
-    <mergeCell ref="C56:M57"/>
-    <mergeCell ref="A58:A59"/>
-    <mergeCell ref="B58:B59"/>
-    <mergeCell ref="C58:M59"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="B60:B61"/>
-    <mergeCell ref="C60:M61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="B62:M63"/>
-  </mergeCells>
-  <hyperlinks>
-    <hyperlink ref="K19" r:id="rId1" display="gtalent1234@gtalent.jp"/>
-  </hyperlinks>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
-  <pageSetup paperSize="9" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="landscape" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader/>
-    <oddFooter/>
-  </headerFooter>
-  <drawing r:id="rId2"/>
-</worksheet>
 </file>
--- a/Tejas_Agrawal_Rirekisho.xlsx
+++ b/Tejas_Agrawal_Rirekisho.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="67" uniqueCount="57">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="59">
   <si>
     <t xml:space="preserve">履 歴 書</t>
   </si>
@@ -40,7 +40,7 @@
     <t xml:space="preserve">ふりがな</t>
   </si>
   <si>
-    <t xml:space="preserve">あぐらわる                 てじゃす</t>
+    <t xml:space="preserve">あぐらわる てじゃす</t>
   </si>
   <si>
     <t xml:space="preserve">氏   名</t>
@@ -115,19 +115,16 @@
     <t xml:space="preserve">制作ゲーム東京ゲームショウ展示</t>
   </si>
   <si>
-    <t xml:space="preserve">インドTHAKUR COLLEGE大学商学士卒業</t>
-  </si>
-  <si>
-    <t xml:space="preserve">配管技能資格 取得</t>
-  </si>
-  <si>
-    <t xml:space="preserve">インドAMITY UNIVERSITY大学院商経営学修士卒業</t>
-  </si>
-  <si>
-    <t xml:space="preserve">日本語学校東洋言語学院入学</t>
-  </si>
-  <si>
-    <t xml:space="preserve">日本語学校東洋言語学院卒業</t>
+    <t xml:space="preserve">インド THAKUR COLLEGE 商学士（B.Com）卒業</t>
+  </si>
+  <si>
+    <t xml:space="preserve">インド AMITY UNIVERSITY IT分野MBA（経営学修士）卒業</t>
+  </si>
+  <si>
+    <t xml:space="preserve">日本語学校 東洋言語学院 入学</t>
+  </si>
+  <si>
+    <t xml:space="preserve">日本語学校 東洋言語学院 卒業</t>
   </si>
   <si>
     <t xml:space="preserve">特技、自己PRなど</t>
@@ -136,26 +133,7 @@
     <t xml:space="preserve">通勤時間</t>
   </si>
   <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="メイリオ"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">専門学校東京クールジャパン・アカデミー</t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="メイリオ"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">ゲーム総合学科ゲームプログラマー専攻入学</t>
-    </r>
+    <t xml:space="preserve">専門学校東京クールジャパン・アカデミー ゲーム総合学科 ゲームプログラマー専攻 入学</t>
   </si>
   <si>
     <r>
@@ -172,11 +150,11 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">分野での</t>
+      <t xml:space="preserve">分野の</t>
     </r>
     <r>
       <rPr>
@@ -192,11 +170,11 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">と監査業務で培った「データ分析力・論理的思考力」を持ち、実践的なプログラミング</t>
+      <t xml:space="preserve">と約</t>
     </r>
     <r>
       <rPr>
@@ -206,18 +184,177 @@
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">(C#, C++, MySQL, Unity)</t>
+      <t xml:space="preserve">4</t>
     </r>
     <r>
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">年間の監査業務で培ったデータ分析力・論理的思考力を基盤とし、専門学校で</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">を習得しました。
-さらに、</t>
+      <t xml:space="preserve">C#</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">C++</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Python</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">JavaScript</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">MySQL</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Unity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">、</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">HTML/CSS</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">を習得しました。</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
+        <family val="2"/>
+        <charset val="1"/>
+      </rPr>
+      <t xml:space="preserve">Unity</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">でゲームを開発し東京ゲームショウに出展する実績に加え、</t>
     </r>
     <r>
       <rPr>
@@ -233,11 +370,31 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">でゼロから構築したポートフォリオサイトを</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">を用いて自作のポートフォリオサイトをゼロから構築するなど、</t>
+      <t xml:space="preserve">Firebase</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">で公開しており、</t>
     </r>
     <r>
       <rPr>
@@ -253,11 +410,11 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">技術や幅広い</t>
+      <t xml:space="preserve">技術にも強い関心を持っています。現在はアルテンジャパンにて半導体装置エンジニアとして勤務しておりますが、入社後に配属先の業務内容が面接時に説明された</t>
     </r>
     <r>
       <rPr>
@@ -273,13 +430,11 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
-        <family val="2"/>
-        <charset val="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">分野へ挑戦しています。
-特定の領域にこだわらず、新しい技術を柔軟に吸収する意欲を持っています。
-現在は半導体エンジニアとして精密な環境で責任感を養っており、これらの強みを活かして</t>
+      <t xml:space="preserve">開発ではなく製造現場での業務となりました。</t>
     </r>
     <r>
       <rPr>
@@ -295,89 +450,100 @@
       <rPr>
         <sz val="11"/>
         <color theme="1"/>
-        <rFont val="Noto Sans JP"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">エンジニア・</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="Calibri"/>
         <family val="2"/>
         <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">全般のエンジニア・プログラマーとして貢献したいと考えております。</t>
+      <t xml:space="preserve">Web</t>
     </r>
-  </si>
-  <si>
-    <t xml:space="preserve">　　　約　　時間　　分</t>
-  </si>
-  <si>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
+        <color theme="1"/>
+        <rFont val="ＭＳ Ｐゴシック"/>
+        <family val="0"/>
+        <charset val="128"/>
+      </rPr>
+      <t xml:space="preserve">開発者・ゲームプログラマーとして、専門知識とプログラミングスキルを活かしたキャリアを追求しております。フロントエンド、バックエンド、ゲーム開発など特定の領域に限定せず、柔軟に技術をキャッチアップし貢献したいと考えております。</t>
+    </r>
+  </si>
+  <si>
+    <t xml:space="preserve">　　　約　　時間　　分</t>
+  </si>
+  <si>
+    <t xml:space="preserve">専門学校東京クールジャパン・アカデミー ゲーム総合学科 ゲームプログラマー専攻 卒業</t>
+  </si>
+  <si>
+    <t xml:space="preserve">扶養家族（配偶者を除く）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">　　　　　　　　　人</t>
+  </si>
+  <si>
+    <t xml:space="preserve">職歴</t>
+  </si>
+  <si>
+    <t xml:space="preserve">配偶者</t>
+  </si>
+  <si>
+    <t xml:space="preserve">配偶者の扶養義務</t>
+  </si>
+  <si>
+    <t xml:space="preserve">TODI TULSYAN &amp; CO.（インド・ムンバイ）入社 監査・マネジメント業務に従事</t>
+  </si>
+  <si>
+    <t xml:space="preserve">有　・　無</t>
+  </si>
+  <si>
+    <t xml:space="preserve">日本への留学のため退職</t>
+  </si>
+  <si>
+    <t xml:space="preserve"> 本人希望記入欄（特に給料・職種・勤務時間・勤務地・その他についての希望などがあれば記入）</t>
+  </si>
+  <si>
+    <t xml:space="preserve">アルテンジャパン株式会社 入社</t>
+  </si>
+  <si>
+    <t xml:space="preserve">職種： ITエンジニア・Web開発者・ゲームプログラマー
+勤務地： 全国可・リモートワーク可
+その他： 入社にあたり転居が可能です。</t>
+  </si>
+  <si>
+    <t xml:space="preserve">    （株式会社SCREENへ配属・半導体装置エンジニアとして従事）</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="メイリオ"/>
         <family val="2"/>
         <charset val="128"/>
       </rPr>
-      <t xml:space="preserve">専門学校東京クールジャパン・アカデミー</t>
+      <t xml:space="preserve">※入社後、配属先の業務内容が面接時に説明されたIT開発ではなく、製造現場での業務</t>
     </r>
     <r>
       <rPr>
-        <sz val="12"/>
+        <sz val="11"/>
         <color theme="1"/>
         <rFont val="メイリオ"/>
         <family val="2"/>
-        <charset val="1"/>
       </rPr>
-      <t xml:space="preserve">ゲーム総合学科ゲームプログラマー専攻卒業</t>
+      <t xml:space="preserve">となり</t>
     </r>
   </si>
   <si>
-    <t xml:space="preserve">扶養家族（配偶者を除く）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">　　　　　　　　　人</t>
-  </si>
-  <si>
-    <t xml:space="preserve">職歴</t>
-  </si>
-  <si>
-    <t xml:space="preserve">配偶者</t>
-  </si>
-  <si>
-    <t xml:space="preserve">配偶者の扶養義務</t>
-  </si>
-  <si>
-    <t xml:space="preserve">TODI TULSYAN &amp; CO. (インド・ムンバイ) 入社 (監査・マネジメント業務に従事)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">有　・　無</t>
-  </si>
-  <si>
-    <t xml:space="preserve">日本への留学のため退職</t>
-  </si>
-  <si>
-    <t xml:space="preserve"> 本人希望記入欄（特に給料・職種・勤務時間・勤務地・その他についての希望などがあれば記入）</t>
-  </si>
-  <si>
-    <t xml:space="preserve">アルテンジャパン株式会社入社</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="メイリオ"/>
-        <family val="2"/>
-        <charset val="128"/>
-      </rPr>
-      <t xml:space="preserve">       </t>
-    </r>
-    <r>
-      <rPr>
-        <sz val="12"/>
-        <color theme="1"/>
-        <rFont val="メイリオ"/>
-        <family val="2"/>
-        <charset val="1"/>
-      </rPr>
-      <t xml:space="preserve">(株式会社SCREENへ配属・半導体装置エンジニアとして従事)</t>
-    </r>
+    <t xml:space="preserve">   ました。ITエンジニアとしてのキャリアを追求するため、早期に軌道修正を図っております。</t>
   </si>
   <si>
     <t xml:space="preserve">現在に至る</t>
@@ -400,7 +566,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="18">
+  <fonts count="17">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -474,13 +640,6 @@
       <charset val="128"/>
     </font>
     <font>
-      <sz val="12"/>
-      <color theme="1"/>
-      <name val="メイリオ"/>
-      <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -490,9 +649,8 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Noto Sans JP"/>
+      <name val="メイリオ"/>
       <family val="2"/>
-      <charset val="1"/>
     </font>
     <font>
       <sz val="8"/>
@@ -994,7 +1152,7 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1022,8 +1180,8 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+    <xf numFmtId="164" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="19" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
@@ -1035,14 +1193,14 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="8" fillId="0" borderId="24" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="14" fillId="0" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1082,9 +1240,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>557280</xdr:colOff>
+      <xdr:colOff>556920</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>62280</xdr:rowOff>
+      <xdr:rowOff>61920</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1094,7 +1252,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6285240" y="177840"/>
-          <a:ext cx="1380240" cy="1779840"/>
+          <a:ext cx="1379880" cy="1779480"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1493,9 +1651,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>577080</xdr:colOff>
+      <xdr:colOff>576720</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>93600</xdr:rowOff>
+      <xdr:rowOff>93240</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1509,7 +1667,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6268680" y="144720"/>
-          <a:ext cx="1416600" cy="1844280"/>
+          <a:ext cx="1416240" cy="1843920"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2688,15 +2846,9 @@
       <c r="K32" s="41"/>
       <c r="L32" s="41"/>
       <c r="M32" s="41"/>
-      <c r="O32" s="14" t="n">
-        <v>2026</v>
-      </c>
-      <c r="P32" s="15" t="n">
-        <v>4</v>
-      </c>
-      <c r="Q32" s="41" t="s">
-        <v>32</v>
-      </c>
+      <c r="O32" s="14"/>
+      <c r="P32" s="15"/>
+      <c r="Q32" s="41"/>
       <c r="R32" s="41"/>
       <c r="S32" s="41"/>
       <c r="T32" s="41"/>
@@ -2744,7 +2896,7 @@
         <v>12</v>
       </c>
       <c r="C34" s="41" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="D34" s="41"/>
       <c r="E34" s="41"/>
@@ -2806,7 +2958,7 @@
         <v>7</v>
       </c>
       <c r="C36" s="41" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="D36" s="41"/>
       <c r="E36" s="41"/>
@@ -2868,7 +3020,7 @@
         <v>3</v>
       </c>
       <c r="C38" s="41" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="D38" s="41"/>
       <c r="E38" s="41"/>
@@ -2909,7 +3061,7 @@
       <c r="L39" s="41"/>
       <c r="M39" s="41"/>
       <c r="O39" s="50" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="P39" s="50"/>
       <c r="Q39" s="50"/>
@@ -2920,7 +3072,7 @@
       <c r="V39" s="50"/>
       <c r="W39" s="50"/>
       <c r="X39" s="50" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="Y39" s="50"/>
       <c r="Z39" s="50"/>
@@ -2934,7 +3086,7 @@
         <v>4</v>
       </c>
       <c r="C40" s="41" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="D40" s="41"/>
       <c r="E40" s="41"/>
@@ -2947,7 +3099,7 @@
       <c r="L40" s="41"/>
       <c r="M40" s="41"/>
       <c r="O40" s="51" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="P40" s="51"/>
       <c r="Q40" s="51"/>
@@ -2958,7 +3110,7 @@
       <c r="V40" s="51"/>
       <c r="W40" s="51"/>
       <c r="X40" s="52" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="Y40" s="52"/>
       <c r="Z40" s="52"/>
@@ -3000,7 +3152,7 @@
         <v>3</v>
       </c>
       <c r="C42" s="41" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="D42" s="41"/>
       <c r="E42" s="41"/>
@@ -3022,7 +3174,7 @@
       <c r="V42" s="51"/>
       <c r="W42" s="51"/>
       <c r="X42" s="50" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="Y42" s="50"/>
       <c r="Z42" s="50"/>
@@ -3052,7 +3204,7 @@
       <c r="V43" s="51"/>
       <c r="W43" s="51"/>
       <c r="X43" s="52" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="Y43" s="52"/>
       <c r="Z43" s="52"/>
@@ -3062,7 +3214,7 @@
       <c r="A44" s="48"/>
       <c r="B44" s="49"/>
       <c r="C44" s="47" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="D44" s="47"/>
       <c r="E44" s="47"/>
@@ -3112,11 +3264,11 @@
       <c r="V45" s="51"/>
       <c r="W45" s="51"/>
       <c r="X45" s="50" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="Y45" s="50"/>
       <c r="Z45" s="50" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AA45" s="50"/>
     </row>
@@ -3128,7 +3280,7 @@
         <v>7</v>
       </c>
       <c r="C46" s="41" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="D46" s="41"/>
       <c r="E46" s="41"/>
@@ -3150,11 +3302,11 @@
       <c r="V46" s="51"/>
       <c r="W46" s="51"/>
       <c r="X46" s="53" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="Y46" s="53"/>
       <c r="Z46" s="54" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="AA46" s="54"/>
     </row>
@@ -3194,7 +3346,7 @@
         <v>11</v>
       </c>
       <c r="C48" s="41" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="D48" s="41"/>
       <c r="E48" s="41"/>
@@ -3235,7 +3387,7 @@
       <c r="L49" s="41"/>
       <c r="M49" s="41"/>
       <c r="O49" s="56" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="P49" s="56"/>
       <c r="Q49" s="56"/>
@@ -3258,7 +3410,7 @@
         <v>4</v>
       </c>
       <c r="C50" s="41" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="D50" s="41"/>
       <c r="E50" s="41"/>
@@ -3298,7 +3450,9 @@
       <c r="K51" s="41"/>
       <c r="L51" s="41"/>
       <c r="M51" s="41"/>
-      <c r="O51" s="57"/>
+      <c r="O51" s="57" t="s">
+        <v>51</v>
+      </c>
       <c r="P51" s="57"/>
       <c r="Q51" s="57"/>
       <c r="R51" s="57"/>
@@ -3373,19 +3527,19 @@
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="48"/>
       <c r="B54" s="49"/>
-      <c r="C54" s="41" t="s">
+      <c r="C54" s="16" t="s">
         <v>53</v>
       </c>
-      <c r="D54" s="41"/>
-      <c r="E54" s="41"/>
-      <c r="F54" s="41"/>
-      <c r="G54" s="41"/>
-      <c r="H54" s="41"/>
-      <c r="I54" s="41"/>
-      <c r="J54" s="41"/>
-      <c r="K54" s="41"/>
-      <c r="L54" s="41"/>
-      <c r="M54" s="41"/>
+      <c r="D54" s="16"/>
+      <c r="E54" s="16"/>
+      <c r="F54" s="16"/>
+      <c r="G54" s="16"/>
+      <c r="H54" s="16"/>
+      <c r="I54" s="16"/>
+      <c r="J54" s="16"/>
+      <c r="K54" s="16"/>
+      <c r="L54" s="16"/>
+      <c r="M54" s="16"/>
       <c r="O54" s="57"/>
       <c r="P54" s="57"/>
       <c r="Q54" s="57"/>
@@ -3403,17 +3557,17 @@
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="48"/>
       <c r="B55" s="49"/>
-      <c r="C55" s="41"/>
-      <c r="D55" s="41"/>
-      <c r="E55" s="41"/>
-      <c r="F55" s="41"/>
-      <c r="G55" s="41"/>
-      <c r="H55" s="41"/>
-      <c r="I55" s="41"/>
-      <c r="J55" s="41"/>
-      <c r="K55" s="41"/>
-      <c r="L55" s="41"/>
-      <c r="M55" s="41"/>
+      <c r="C55" s="16"/>
+      <c r="D55" s="16"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="16"/>
+      <c r="G55" s="16"/>
+      <c r="H55" s="16"/>
+      <c r="I55" s="16"/>
+      <c r="J55" s="16"/>
+      <c r="K55" s="16"/>
+      <c r="L55" s="16"/>
+      <c r="M55" s="16"/>
       <c r="O55" s="57"/>
       <c r="P55" s="57"/>
       <c r="Q55" s="57"/>
@@ -3489,7 +3643,9 @@
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="48"/>
       <c r="B58" s="49"/>
-      <c r="C58" s="41"/>
+      <c r="C58" s="41" t="s">
+        <v>55</v>
+      </c>
       <c r="D58" s="41"/>
       <c r="E58" s="41"/>
       <c r="F58" s="41"/>
@@ -3545,7 +3701,9 @@
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A60" s="59"/>
       <c r="B60" s="60"/>
-      <c r="C60" s="61"/>
+      <c r="C60" s="61" t="s">
+        <v>56</v>
+      </c>
       <c r="D60" s="61"/>
       <c r="E60" s="61"/>
       <c r="F60" s="61"/>
@@ -3600,10 +3758,10 @@
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A62" s="62" t="s">
-        <v>55</v>
+        <v>57</v>
       </c>
       <c r="B62" s="63" t="s">
-        <v>56</v>
+        <v>58</v>
       </c>
       <c r="C62" s="63"/>
       <c r="D62" s="63"/>

--- a/Tejas_Agrawal_Rirekisho.xlsx
+++ b/Tejas_Agrawal_Rirekisho.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="70" uniqueCount="60">
   <si>
     <t xml:space="preserve">履 歴 書</t>
   </si>
@@ -116,6 +116,35 @@
   </si>
   <si>
     <t xml:space="preserve">インド THAKUR COLLEGE 商学士（B.Com）卒業</t>
+  </si>
+  <si>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">日本語能力試験</t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Times New Roman"/>
+        <family val="1"/>
+      </rPr>
+      <t xml:space="preserve">(JLPT)N1 </t>
+    </r>
+    <r>
+      <rPr>
+        <sz val="10"/>
+        <color theme="1"/>
+        <rFont val="Segoe UI"/>
+        <family val="2"/>
+      </rPr>
+      <t xml:space="preserve">受験予定 </t>
+    </r>
   </si>
   <si>
     <t xml:space="preserve">インド AMITY UNIVERSITY IT分野MBA（経営学修士）卒業</t>
@@ -538,6 +567,7 @@
         <color theme="1"/>
         <rFont val="メイリオ"/>
         <family val="2"/>
+        <charset val="1"/>
       </rPr>
       <t xml:space="preserve">となり</t>
     </r>
@@ -566,7 +596,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="17">
+  <fonts count="19">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -640,6 +670,18 @@
       <charset val="128"/>
     </font>
     <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Segoe UI"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Times New Roman"/>
+      <family val="1"/>
+    </font>
+    <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="Calibri"/>
@@ -651,6 +693,7 @@
       <color theme="1"/>
       <name val="メイリオ"/>
       <family val="2"/>
+      <charset val="1"/>
     </font>
     <font>
       <sz val="8"/>
@@ -947,7 +990,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="67">
+  <cellXfs count="68">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1148,11 +1191,15 @@
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
+    <xf numFmtId="164" fontId="11" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+      <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
     <xf numFmtId="164" fontId="6" fillId="0" borderId="21" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="11" fillId="0" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="13" fillId="0" borderId="27" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1180,7 +1227,7 @@
       <alignment horizontal="left" vertical="top" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="14" fillId="0" borderId="8" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1196,11 +1243,11 @@
       <alignment horizontal="right" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="center" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="13" fillId="0" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
+    <xf numFmtId="164" fontId="15" fillId="0" borderId="32" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="true">
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="true" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1240,9 +1287,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>556920</xdr:colOff>
+      <xdr:colOff>556560</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>61920</xdr:rowOff>
+      <xdr:rowOff>61560</xdr:rowOff>
     </xdr:to>
     <xdr:sp>
       <xdr:nvSpPr>
@@ -1252,7 +1299,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6285240" y="177840"/>
-          <a:ext cx="1379880" cy="1779480"/>
+          <a:ext cx="1379520" cy="1779120"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1651,9 +1698,9 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>12</xdr:col>
-      <xdr:colOff>576720</xdr:colOff>
+      <xdr:colOff>576360</xdr:colOff>
       <xdr:row>11</xdr:row>
-      <xdr:rowOff>93240</xdr:rowOff>
+      <xdr:rowOff>92880</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -1667,7 +1714,7 @@
       <xdr:spPr>
         <a:xfrm>
           <a:off x="6268680" y="144720"/>
-          <a:ext cx="1416240" cy="1843920"/>
+          <a:ext cx="1415880" cy="1843560"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -2846,19 +2893,25 @@
       <c r="K32" s="41"/>
       <c r="L32" s="41"/>
       <c r="M32" s="41"/>
-      <c r="O32" s="14"/>
-      <c r="P32" s="15"/>
-      <c r="Q32" s="41"/>
-      <c r="R32" s="41"/>
-      <c r="S32" s="41"/>
-      <c r="T32" s="41"/>
-      <c r="U32" s="41"/>
-      <c r="V32" s="41"/>
-      <c r="W32" s="41"/>
-      <c r="X32" s="41"/>
-      <c r="Y32" s="41"/>
-      <c r="Z32" s="41"/>
-      <c r="AA32" s="41"/>
+      <c r="O32" s="14" t="n">
+        <v>2026</v>
+      </c>
+      <c r="P32" s="15" t="n">
+        <v>12</v>
+      </c>
+      <c r="Q32" s="50" t="s">
+        <v>32</v>
+      </c>
+      <c r="R32" s="50"/>
+      <c r="S32" s="50"/>
+      <c r="T32" s="50"/>
+      <c r="U32" s="50"/>
+      <c r="V32" s="50"/>
+      <c r="W32" s="50"/>
+      <c r="X32" s="50"/>
+      <c r="Y32" s="50"/>
+      <c r="Z32" s="50"/>
+      <c r="AA32" s="50"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="48"/>
@@ -2876,17 +2929,17 @@
       <c r="M33" s="41"/>
       <c r="O33" s="14"/>
       <c r="P33" s="15"/>
-      <c r="Q33" s="41"/>
-      <c r="R33" s="41"/>
-      <c r="S33" s="41"/>
-      <c r="T33" s="41"/>
-      <c r="U33" s="41"/>
-      <c r="V33" s="41"/>
-      <c r="W33" s="41"/>
-      <c r="X33" s="41"/>
-      <c r="Y33" s="41"/>
-      <c r="Z33" s="41"/>
-      <c r="AA33" s="41"/>
+      <c r="Q33" s="50"/>
+      <c r="R33" s="50"/>
+      <c r="S33" s="50"/>
+      <c r="T33" s="50"/>
+      <c r="U33" s="50"/>
+      <c r="V33" s="50"/>
+      <c r="W33" s="50"/>
+      <c r="X33" s="50"/>
+      <c r="Y33" s="50"/>
+      <c r="Z33" s="50"/>
+      <c r="AA33" s="50"/>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A34" s="48" t="n">
@@ -2896,7 +2949,7 @@
         <v>12</v>
       </c>
       <c r="C34" s="41" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="D34" s="41"/>
       <c r="E34" s="41"/>
@@ -2958,7 +3011,7 @@
         <v>7</v>
       </c>
       <c r="C36" s="41" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="D36" s="41"/>
       <c r="E36" s="41"/>
@@ -3020,7 +3073,7 @@
         <v>3</v>
       </c>
       <c r="C38" s="41" t="s">
-        <v>34</v>
+        <v>35</v>
       </c>
       <c r="D38" s="41"/>
       <c r="E38" s="41"/>
@@ -3060,23 +3113,23 @@
       <c r="K39" s="41"/>
       <c r="L39" s="41"/>
       <c r="M39" s="41"/>
-      <c r="O39" s="50" t="s">
-        <v>35</v>
-      </c>
-      <c r="P39" s="50"/>
-      <c r="Q39" s="50"/>
-      <c r="R39" s="50"/>
-      <c r="S39" s="50"/>
-      <c r="T39" s="50"/>
-      <c r="U39" s="50"/>
-      <c r="V39" s="50"/>
-      <c r="W39" s="50"/>
-      <c r="X39" s="50" t="s">
+      <c r="O39" s="51" t="s">
         <v>36</v>
       </c>
-      <c r="Y39" s="50"/>
-      <c r="Z39" s="50"/>
-      <c r="AA39" s="50"/>
+      <c r="P39" s="51"/>
+      <c r="Q39" s="51"/>
+      <c r="R39" s="51"/>
+      <c r="S39" s="51"/>
+      <c r="T39" s="51"/>
+      <c r="U39" s="51"/>
+      <c r="V39" s="51"/>
+      <c r="W39" s="51"/>
+      <c r="X39" s="51" t="s">
+        <v>37</v>
+      </c>
+      <c r="Y39" s="51"/>
+      <c r="Z39" s="51"/>
+      <c r="AA39" s="51"/>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="48" t="n">
@@ -3086,7 +3139,7 @@
         <v>4</v>
       </c>
       <c r="C40" s="41" t="s">
-        <v>37</v>
+        <v>38</v>
       </c>
       <c r="D40" s="41"/>
       <c r="E40" s="41"/>
@@ -3098,23 +3151,23 @@
       <c r="K40" s="41"/>
       <c r="L40" s="41"/>
       <c r="M40" s="41"/>
-      <c r="O40" s="51" t="s">
-        <v>38</v>
-      </c>
-      <c r="P40" s="51"/>
-      <c r="Q40" s="51"/>
-      <c r="R40" s="51"/>
-      <c r="S40" s="51"/>
-      <c r="T40" s="51"/>
-      <c r="U40" s="51"/>
-      <c r="V40" s="51"/>
-      <c r="W40" s="51"/>
-      <c r="X40" s="52" t="s">
+      <c r="O40" s="52" t="s">
         <v>39</v>
       </c>
-      <c r="Y40" s="52"/>
-      <c r="Z40" s="52"/>
-      <c r="AA40" s="52"/>
+      <c r="P40" s="52"/>
+      <c r="Q40" s="52"/>
+      <c r="R40" s="52"/>
+      <c r="S40" s="52"/>
+      <c r="T40" s="52"/>
+      <c r="U40" s="52"/>
+      <c r="V40" s="52"/>
+      <c r="W40" s="52"/>
+      <c r="X40" s="53" t="s">
+        <v>40</v>
+      </c>
+      <c r="Y40" s="53"/>
+      <c r="Z40" s="53"/>
+      <c r="AA40" s="53"/>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="48"/>
@@ -3130,19 +3183,19 @@
       <c r="K41" s="41"/>
       <c r="L41" s="41"/>
       <c r="M41" s="41"/>
-      <c r="O41" s="51"/>
-      <c r="P41" s="51"/>
-      <c r="Q41" s="51"/>
-      <c r="R41" s="51"/>
-      <c r="S41" s="51"/>
-      <c r="T41" s="51"/>
-      <c r="U41" s="51"/>
-      <c r="V41" s="51"/>
-      <c r="W41" s="51"/>
-      <c r="X41" s="52"/>
-      <c r="Y41" s="52"/>
-      <c r="Z41" s="52"/>
-      <c r="AA41" s="52"/>
+      <c r="O41" s="52"/>
+      <c r="P41" s="52"/>
+      <c r="Q41" s="52"/>
+      <c r="R41" s="52"/>
+      <c r="S41" s="52"/>
+      <c r="T41" s="52"/>
+      <c r="U41" s="52"/>
+      <c r="V41" s="52"/>
+      <c r="W41" s="52"/>
+      <c r="X41" s="53"/>
+      <c r="Y41" s="53"/>
+      <c r="Z41" s="53"/>
+      <c r="AA41" s="53"/>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="48" t="n">
@@ -3152,7 +3205,7 @@
         <v>3</v>
       </c>
       <c r="C42" s="41" t="s">
-        <v>40</v>
+        <v>41</v>
       </c>
       <c r="D42" s="41"/>
       <c r="E42" s="41"/>
@@ -3164,21 +3217,21 @@
       <c r="K42" s="41"/>
       <c r="L42" s="41"/>
       <c r="M42" s="41"/>
-      <c r="O42" s="51"/>
-      <c r="P42" s="51"/>
-      <c r="Q42" s="51"/>
-      <c r="R42" s="51"/>
-      <c r="S42" s="51"/>
-      <c r="T42" s="51"/>
-      <c r="U42" s="51"/>
-      <c r="V42" s="51"/>
-      <c r="W42" s="51"/>
-      <c r="X42" s="50" t="s">
-        <v>41</v>
-      </c>
-      <c r="Y42" s="50"/>
-      <c r="Z42" s="50"/>
-      <c r="AA42" s="50"/>
+      <c r="O42" s="52"/>
+      <c r="P42" s="52"/>
+      <c r="Q42" s="52"/>
+      <c r="R42" s="52"/>
+      <c r="S42" s="52"/>
+      <c r="T42" s="52"/>
+      <c r="U42" s="52"/>
+      <c r="V42" s="52"/>
+      <c r="W42" s="52"/>
+      <c r="X42" s="51" t="s">
+        <v>42</v>
+      </c>
+      <c r="Y42" s="51"/>
+      <c r="Z42" s="51"/>
+      <c r="AA42" s="51"/>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="48"/>
@@ -3194,27 +3247,27 @@
       <c r="K43" s="41"/>
       <c r="L43" s="41"/>
       <c r="M43" s="41"/>
-      <c r="O43" s="51"/>
-      <c r="P43" s="51"/>
-      <c r="Q43" s="51"/>
-      <c r="R43" s="51"/>
-      <c r="S43" s="51"/>
-      <c r="T43" s="51"/>
-      <c r="U43" s="51"/>
-      <c r="V43" s="51"/>
-      <c r="W43" s="51"/>
-      <c r="X43" s="52" t="s">
-        <v>42</v>
-      </c>
-      <c r="Y43" s="52"/>
-      <c r="Z43" s="52"/>
-      <c r="AA43" s="52"/>
+      <c r="O43" s="52"/>
+      <c r="P43" s="52"/>
+      <c r="Q43" s="52"/>
+      <c r="R43" s="52"/>
+      <c r="S43" s="52"/>
+      <c r="T43" s="52"/>
+      <c r="U43" s="52"/>
+      <c r="V43" s="52"/>
+      <c r="W43" s="52"/>
+      <c r="X43" s="53" t="s">
+        <v>43</v>
+      </c>
+      <c r="Y43" s="53"/>
+      <c r="Z43" s="53"/>
+      <c r="AA43" s="53"/>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="48"/>
       <c r="B44" s="49"/>
       <c r="C44" s="47" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D44" s="47"/>
       <c r="E44" s="47"/>
@@ -3226,19 +3279,19 @@
       <c r="K44" s="47"/>
       <c r="L44" s="47"/>
       <c r="M44" s="47"/>
-      <c r="O44" s="51"/>
-      <c r="P44" s="51"/>
-      <c r="Q44" s="51"/>
-      <c r="R44" s="51"/>
-      <c r="S44" s="51"/>
-      <c r="T44" s="51"/>
-      <c r="U44" s="51"/>
-      <c r="V44" s="51"/>
-      <c r="W44" s="51"/>
-      <c r="X44" s="52"/>
-      <c r="Y44" s="52"/>
-      <c r="Z44" s="52"/>
-      <c r="AA44" s="52"/>
+      <c r="O44" s="52"/>
+      <c r="P44" s="52"/>
+      <c r="Q44" s="52"/>
+      <c r="R44" s="52"/>
+      <c r="S44" s="52"/>
+      <c r="T44" s="52"/>
+      <c r="U44" s="52"/>
+      <c r="V44" s="52"/>
+      <c r="W44" s="52"/>
+      <c r="X44" s="53"/>
+      <c r="Y44" s="53"/>
+      <c r="Z44" s="53"/>
+      <c r="AA44" s="53"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="48"/>
@@ -3254,23 +3307,23 @@
       <c r="K45" s="47"/>
       <c r="L45" s="47"/>
       <c r="M45" s="47"/>
-      <c r="O45" s="51"/>
-      <c r="P45" s="51"/>
-      <c r="Q45" s="51"/>
-      <c r="R45" s="51"/>
-      <c r="S45" s="51"/>
-      <c r="T45" s="51"/>
-      <c r="U45" s="51"/>
-      <c r="V45" s="51"/>
-      <c r="W45" s="51"/>
-      <c r="X45" s="50" t="s">
-        <v>44</v>
-      </c>
-      <c r="Y45" s="50"/>
-      <c r="Z45" s="50" t="s">
+      <c r="O45" s="52"/>
+      <c r="P45" s="52"/>
+      <c r="Q45" s="52"/>
+      <c r="R45" s="52"/>
+      <c r="S45" s="52"/>
+      <c r="T45" s="52"/>
+      <c r="U45" s="52"/>
+      <c r="V45" s="52"/>
+      <c r="W45" s="52"/>
+      <c r="X45" s="51" t="s">
         <v>45</v>
       </c>
-      <c r="AA45" s="50"/>
+      <c r="Y45" s="51"/>
+      <c r="Z45" s="51" t="s">
+        <v>46</v>
+      </c>
+      <c r="AA45" s="51"/>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A46" s="48" t="n">
@@ -3280,7 +3333,7 @@
         <v>7</v>
       </c>
       <c r="C46" s="41" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="D46" s="41"/>
       <c r="E46" s="41"/>
@@ -3292,23 +3345,23 @@
       <c r="K46" s="41"/>
       <c r="L46" s="41"/>
       <c r="M46" s="41"/>
-      <c r="O46" s="51"/>
-      <c r="P46" s="51"/>
-      <c r="Q46" s="51"/>
-      <c r="R46" s="51"/>
-      <c r="S46" s="51"/>
-      <c r="T46" s="51"/>
-      <c r="U46" s="51"/>
-      <c r="V46" s="51"/>
-      <c r="W46" s="51"/>
-      <c r="X46" s="53" t="s">
-        <v>47</v>
-      </c>
-      <c r="Y46" s="53"/>
-      <c r="Z46" s="54" t="s">
-        <v>47</v>
-      </c>
-      <c r="AA46" s="54"/>
+      <c r="O46" s="52"/>
+      <c r="P46" s="52"/>
+      <c r="Q46" s="52"/>
+      <c r="R46" s="52"/>
+      <c r="S46" s="52"/>
+      <c r="T46" s="52"/>
+      <c r="U46" s="52"/>
+      <c r="V46" s="52"/>
+      <c r="W46" s="52"/>
+      <c r="X46" s="54" t="s">
+        <v>48</v>
+      </c>
+      <c r="Y46" s="54"/>
+      <c r="Z46" s="55" t="s">
+        <v>48</v>
+      </c>
+      <c r="AA46" s="55"/>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="48"/>
@@ -3324,19 +3377,19 @@
       <c r="K47" s="41"/>
       <c r="L47" s="41"/>
       <c r="M47" s="41"/>
-      <c r="O47" s="51"/>
-      <c r="P47" s="51"/>
-      <c r="Q47" s="51"/>
-      <c r="R47" s="51"/>
-      <c r="S47" s="51"/>
-      <c r="T47" s="51"/>
-      <c r="U47" s="51"/>
-      <c r="V47" s="51"/>
-      <c r="W47" s="51"/>
-      <c r="X47" s="53"/>
-      <c r="Y47" s="53"/>
-      <c r="Z47" s="54"/>
-      <c r="AA47" s="54"/>
+      <c r="O47" s="52"/>
+      <c r="P47" s="52"/>
+      <c r="Q47" s="52"/>
+      <c r="R47" s="52"/>
+      <c r="S47" s="52"/>
+      <c r="T47" s="52"/>
+      <c r="U47" s="52"/>
+      <c r="V47" s="52"/>
+      <c r="W47" s="52"/>
+      <c r="X47" s="54"/>
+      <c r="Y47" s="54"/>
+      <c r="Z47" s="55"/>
+      <c r="AA47" s="55"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A48" s="48" t="n">
@@ -3346,7 +3399,7 @@
         <v>11</v>
       </c>
       <c r="C48" s="41" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="D48" s="41"/>
       <c r="E48" s="41"/>
@@ -3367,10 +3420,10 @@
       <c r="U48" s="7"/>
       <c r="V48" s="7"/>
       <c r="W48" s="7"/>
-      <c r="X48" s="55"/>
-      <c r="Y48" s="55"/>
-      <c r="Z48" s="55"/>
-      <c r="AA48" s="55"/>
+      <c r="X48" s="56"/>
+      <c r="Y48" s="56"/>
+      <c r="Z48" s="56"/>
+      <c r="AA48" s="56"/>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A49" s="48"/>
@@ -3386,21 +3439,21 @@
       <c r="K49" s="41"/>
       <c r="L49" s="41"/>
       <c r="M49" s="41"/>
-      <c r="O49" s="56" t="s">
-        <v>49</v>
-      </c>
-      <c r="P49" s="56"/>
-      <c r="Q49" s="56"/>
-      <c r="R49" s="56"/>
-      <c r="S49" s="56"/>
-      <c r="T49" s="56"/>
-      <c r="U49" s="56"/>
-      <c r="V49" s="56"/>
-      <c r="W49" s="56"/>
-      <c r="X49" s="56"/>
-      <c r="Y49" s="56"/>
-      <c r="Z49" s="56"/>
-      <c r="AA49" s="56"/>
+      <c r="O49" s="57" t="s">
+        <v>50</v>
+      </c>
+      <c r="P49" s="57"/>
+      <c r="Q49" s="57"/>
+      <c r="R49" s="57"/>
+      <c r="S49" s="57"/>
+      <c r="T49" s="57"/>
+      <c r="U49" s="57"/>
+      <c r="V49" s="57"/>
+      <c r="W49" s="57"/>
+      <c r="X49" s="57"/>
+      <c r="Y49" s="57"/>
+      <c r="Z49" s="57"/>
+      <c r="AA49" s="57"/>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A50" s="48" t="n">
@@ -3410,7 +3463,7 @@
         <v>4</v>
       </c>
       <c r="C50" s="41" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="D50" s="41"/>
       <c r="E50" s="41"/>
@@ -3422,19 +3475,19 @@
       <c r="K50" s="41"/>
       <c r="L50" s="41"/>
       <c r="M50" s="41"/>
-      <c r="O50" s="56"/>
-      <c r="P50" s="56"/>
-      <c r="Q50" s="56"/>
-      <c r="R50" s="56"/>
-      <c r="S50" s="56"/>
-      <c r="T50" s="56"/>
-      <c r="U50" s="56"/>
-      <c r="V50" s="56"/>
-      <c r="W50" s="56"/>
-      <c r="X50" s="56"/>
-      <c r="Y50" s="56"/>
-      <c r="Z50" s="56"/>
-      <c r="AA50" s="56"/>
+      <c r="O50" s="57"/>
+      <c r="P50" s="57"/>
+      <c r="Q50" s="57"/>
+      <c r="R50" s="57"/>
+      <c r="S50" s="57"/>
+      <c r="T50" s="57"/>
+      <c r="U50" s="57"/>
+      <c r="V50" s="57"/>
+      <c r="W50" s="57"/>
+      <c r="X50" s="57"/>
+      <c r="Y50" s="57"/>
+      <c r="Z50" s="57"/>
+      <c r="AA50" s="57"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A51" s="48"/>
@@ -3450,27 +3503,27 @@
       <c r="K51" s="41"/>
       <c r="L51" s="41"/>
       <c r="M51" s="41"/>
-      <c r="O51" s="57" t="s">
-        <v>51</v>
-      </c>
-      <c r="P51" s="57"/>
-      <c r="Q51" s="57"/>
-      <c r="R51" s="57"/>
-      <c r="S51" s="57"/>
-      <c r="T51" s="57"/>
-      <c r="U51" s="57"/>
-      <c r="V51" s="57"/>
-      <c r="W51" s="57"/>
-      <c r="X51" s="57"/>
-      <c r="Y51" s="57"/>
-      <c r="Z51" s="57"/>
-      <c r="AA51" s="57"/>
+      <c r="O51" s="58" t="s">
+        <v>52</v>
+      </c>
+      <c r="P51" s="58"/>
+      <c r="Q51" s="58"/>
+      <c r="R51" s="58"/>
+      <c r="S51" s="58"/>
+      <c r="T51" s="58"/>
+      <c r="U51" s="58"/>
+      <c r="V51" s="58"/>
+      <c r="W51" s="58"/>
+      <c r="X51" s="58"/>
+      <c r="Y51" s="58"/>
+      <c r="Z51" s="58"/>
+      <c r="AA51" s="58"/>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A52" s="48"/>
       <c r="B52" s="49"/>
       <c r="C52" s="41" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="D52" s="41"/>
       <c r="E52" s="41"/>
@@ -3482,19 +3535,19 @@
       <c r="K52" s="41"/>
       <c r="L52" s="41"/>
       <c r="M52" s="41"/>
-      <c r="O52" s="57"/>
-      <c r="P52" s="57"/>
-      <c r="Q52" s="57"/>
-      <c r="R52" s="57"/>
-      <c r="S52" s="57"/>
-      <c r="T52" s="57"/>
-      <c r="U52" s="57"/>
-      <c r="V52" s="57"/>
-      <c r="W52" s="57"/>
-      <c r="X52" s="57"/>
-      <c r="Y52" s="57"/>
-      <c r="Z52" s="57"/>
-      <c r="AA52" s="57"/>
+      <c r="O52" s="58"/>
+      <c r="P52" s="58"/>
+      <c r="Q52" s="58"/>
+      <c r="R52" s="58"/>
+      <c r="S52" s="58"/>
+      <c r="T52" s="58"/>
+      <c r="U52" s="58"/>
+      <c r="V52" s="58"/>
+      <c r="W52" s="58"/>
+      <c r="X52" s="58"/>
+      <c r="Y52" s="58"/>
+      <c r="Z52" s="58"/>
+      <c r="AA52" s="58"/>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A53" s="48"/>
@@ -3510,25 +3563,25 @@
       <c r="K53" s="41"/>
       <c r="L53" s="41"/>
       <c r="M53" s="41"/>
-      <c r="O53" s="57"/>
-      <c r="P53" s="57"/>
-      <c r="Q53" s="57"/>
-      <c r="R53" s="57"/>
-      <c r="S53" s="57"/>
-      <c r="T53" s="57"/>
-      <c r="U53" s="57"/>
-      <c r="V53" s="57"/>
-      <c r="W53" s="57"/>
-      <c r="X53" s="57"/>
-      <c r="Y53" s="57"/>
-      <c r="Z53" s="57"/>
-      <c r="AA53" s="57"/>
+      <c r="O53" s="58"/>
+      <c r="P53" s="58"/>
+      <c r="Q53" s="58"/>
+      <c r="R53" s="58"/>
+      <c r="S53" s="58"/>
+      <c r="T53" s="58"/>
+      <c r="U53" s="58"/>
+      <c r="V53" s="58"/>
+      <c r="W53" s="58"/>
+      <c r="X53" s="58"/>
+      <c r="Y53" s="58"/>
+      <c r="Z53" s="58"/>
+      <c r="AA53" s="58"/>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A54" s="48"/>
       <c r="B54" s="49"/>
       <c r="C54" s="16" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="D54" s="16"/>
       <c r="E54" s="16"/>
@@ -3540,19 +3593,19 @@
       <c r="K54" s="16"/>
       <c r="L54" s="16"/>
       <c r="M54" s="16"/>
-      <c r="O54" s="57"/>
-      <c r="P54" s="57"/>
-      <c r="Q54" s="57"/>
-      <c r="R54" s="57"/>
-      <c r="S54" s="57"/>
-      <c r="T54" s="57"/>
-      <c r="U54" s="57"/>
-      <c r="V54" s="57"/>
-      <c r="W54" s="57"/>
-      <c r="X54" s="57"/>
-      <c r="Y54" s="57"/>
-      <c r="Z54" s="57"/>
-      <c r="AA54" s="57"/>
+      <c r="O54" s="58"/>
+      <c r="P54" s="58"/>
+      <c r="Q54" s="58"/>
+      <c r="R54" s="58"/>
+      <c r="S54" s="58"/>
+      <c r="T54" s="58"/>
+      <c r="U54" s="58"/>
+      <c r="V54" s="58"/>
+      <c r="W54" s="58"/>
+      <c r="X54" s="58"/>
+      <c r="Y54" s="58"/>
+      <c r="Z54" s="58"/>
+      <c r="AA54" s="58"/>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A55" s="48"/>
@@ -3568,83 +3621,83 @@
       <c r="K55" s="16"/>
       <c r="L55" s="16"/>
       <c r="M55" s="16"/>
-      <c r="O55" s="57"/>
-      <c r="P55" s="57"/>
-      <c r="Q55" s="57"/>
-      <c r="R55" s="57"/>
-      <c r="S55" s="57"/>
-      <c r="T55" s="57"/>
-      <c r="U55" s="57"/>
-      <c r="V55" s="57"/>
-      <c r="W55" s="57"/>
-      <c r="X55" s="57"/>
-      <c r="Y55" s="57"/>
-      <c r="Z55" s="57"/>
-      <c r="AA55" s="57"/>
+      <c r="O55" s="58"/>
+      <c r="P55" s="58"/>
+      <c r="Q55" s="58"/>
+      <c r="R55" s="58"/>
+      <c r="S55" s="58"/>
+      <c r="T55" s="58"/>
+      <c r="U55" s="58"/>
+      <c r="V55" s="58"/>
+      <c r="W55" s="58"/>
+      <c r="X55" s="58"/>
+      <c r="Y55" s="58"/>
+      <c r="Z55" s="58"/>
+      <c r="AA55" s="58"/>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A56" s="48"/>
       <c r="B56" s="49"/>
-      <c r="C56" s="58" t="s">
-        <v>54</v>
-      </c>
-      <c r="D56" s="58"/>
-      <c r="E56" s="58"/>
-      <c r="F56" s="58"/>
-      <c r="G56" s="58"/>
-      <c r="H56" s="58"/>
-      <c r="I56" s="58"/>
-      <c r="J56" s="58"/>
-      <c r="K56" s="58"/>
-      <c r="L56" s="58"/>
-      <c r="M56" s="58"/>
-      <c r="O56" s="57"/>
-      <c r="P56" s="57"/>
-      <c r="Q56" s="57"/>
-      <c r="R56" s="57"/>
-      <c r="S56" s="57"/>
-      <c r="T56" s="57"/>
-      <c r="U56" s="57"/>
-      <c r="V56" s="57"/>
-      <c r="W56" s="57"/>
-      <c r="X56" s="57"/>
-      <c r="Y56" s="57"/>
-      <c r="Z56" s="57"/>
-      <c r="AA56" s="57"/>
+      <c r="C56" s="59" t="s">
+        <v>55</v>
+      </c>
+      <c r="D56" s="59"/>
+      <c r="E56" s="59"/>
+      <c r="F56" s="59"/>
+      <c r="G56" s="59"/>
+      <c r="H56" s="59"/>
+      <c r="I56" s="59"/>
+      <c r="J56" s="59"/>
+      <c r="K56" s="59"/>
+      <c r="L56" s="59"/>
+      <c r="M56" s="59"/>
+      <c r="O56" s="58"/>
+      <c r="P56" s="58"/>
+      <c r="Q56" s="58"/>
+      <c r="R56" s="58"/>
+      <c r="S56" s="58"/>
+      <c r="T56" s="58"/>
+      <c r="U56" s="58"/>
+      <c r="V56" s="58"/>
+      <c r="W56" s="58"/>
+      <c r="X56" s="58"/>
+      <c r="Y56" s="58"/>
+      <c r="Z56" s="58"/>
+      <c r="AA56" s="58"/>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A57" s="48"/>
       <c r="B57" s="49"/>
-      <c r="C57" s="58"/>
-      <c r="D57" s="58"/>
-      <c r="E57" s="58"/>
-      <c r="F57" s="58"/>
-      <c r="G57" s="58"/>
-      <c r="H57" s="58"/>
-      <c r="I57" s="58"/>
-      <c r="J57" s="58"/>
-      <c r="K57" s="58"/>
-      <c r="L57" s="58"/>
-      <c r="M57" s="58"/>
-      <c r="O57" s="57"/>
-      <c r="P57" s="57"/>
-      <c r="Q57" s="57"/>
-      <c r="R57" s="57"/>
-      <c r="S57" s="57"/>
-      <c r="T57" s="57"/>
-      <c r="U57" s="57"/>
-      <c r="V57" s="57"/>
-      <c r="W57" s="57"/>
-      <c r="X57" s="57"/>
-      <c r="Y57" s="57"/>
-      <c r="Z57" s="57"/>
-      <c r="AA57" s="57"/>
+      <c r="C57" s="59"/>
+      <c r="D57" s="59"/>
+      <c r="E57" s="59"/>
+      <c r="F57" s="59"/>
+      <c r="G57" s="59"/>
+      <c r="H57" s="59"/>
+      <c r="I57" s="59"/>
+      <c r="J57" s="59"/>
+      <c r="K57" s="59"/>
+      <c r="L57" s="59"/>
+      <c r="M57" s="59"/>
+      <c r="O57" s="58"/>
+      <c r="P57" s="58"/>
+      <c r="Q57" s="58"/>
+      <c r="R57" s="58"/>
+      <c r="S57" s="58"/>
+      <c r="T57" s="58"/>
+      <c r="U57" s="58"/>
+      <c r="V57" s="58"/>
+      <c r="W57" s="58"/>
+      <c r="X57" s="58"/>
+      <c r="Y57" s="58"/>
+      <c r="Z57" s="58"/>
+      <c r="AA57" s="58"/>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A58" s="48"/>
       <c r="B58" s="49"/>
       <c r="C58" s="41" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="D58" s="41"/>
       <c r="E58" s="41"/>
@@ -3656,19 +3709,19 @@
       <c r="K58" s="41"/>
       <c r="L58" s="41"/>
       <c r="M58" s="41"/>
-      <c r="O58" s="57"/>
-      <c r="P58" s="57"/>
-      <c r="Q58" s="57"/>
-      <c r="R58" s="57"/>
-      <c r="S58" s="57"/>
-      <c r="T58" s="57"/>
-      <c r="U58" s="57"/>
-      <c r="V58" s="57"/>
-      <c r="W58" s="57"/>
-      <c r="X58" s="57"/>
-      <c r="Y58" s="57"/>
-      <c r="Z58" s="57"/>
-      <c r="AA58" s="57"/>
+      <c r="O58" s="58"/>
+      <c r="P58" s="58"/>
+      <c r="Q58" s="58"/>
+      <c r="R58" s="58"/>
+      <c r="S58" s="58"/>
+      <c r="T58" s="58"/>
+      <c r="U58" s="58"/>
+      <c r="V58" s="58"/>
+      <c r="W58" s="58"/>
+      <c r="X58" s="58"/>
+      <c r="Y58" s="58"/>
+      <c r="Z58" s="58"/>
+      <c r="AA58" s="58"/>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A59" s="48"/>
@@ -3684,254 +3737,254 @@
       <c r="K59" s="41"/>
       <c r="L59" s="41"/>
       <c r="M59" s="41"/>
-      <c r="O59" s="57"/>
-      <c r="P59" s="57"/>
-      <c r="Q59" s="57"/>
-      <c r="R59" s="57"/>
-      <c r="S59" s="57"/>
-      <c r="T59" s="57"/>
-      <c r="U59" s="57"/>
-      <c r="V59" s="57"/>
-      <c r="W59" s="57"/>
-      <c r="X59" s="57"/>
-      <c r="Y59" s="57"/>
-      <c r="Z59" s="57"/>
-      <c r="AA59" s="57"/>
+      <c r="O59" s="58"/>
+      <c r="P59" s="58"/>
+      <c r="Q59" s="58"/>
+      <c r="R59" s="58"/>
+      <c r="S59" s="58"/>
+      <c r="T59" s="58"/>
+      <c r="U59" s="58"/>
+      <c r="V59" s="58"/>
+      <c r="W59" s="58"/>
+      <c r="X59" s="58"/>
+      <c r="Y59" s="58"/>
+      <c r="Z59" s="58"/>
+      <c r="AA59" s="58"/>
     </row>
     <row r="60" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A60" s="59"/>
-      <c r="B60" s="60"/>
-      <c r="C60" s="61" t="s">
-        <v>56</v>
-      </c>
-      <c r="D60" s="61"/>
-      <c r="E60" s="61"/>
-      <c r="F60" s="61"/>
-      <c r="G60" s="61"/>
-      <c r="H60" s="61"/>
-      <c r="I60" s="61"/>
-      <c r="J60" s="61"/>
-      <c r="K60" s="61"/>
-      <c r="L60" s="61"/>
-      <c r="M60" s="61"/>
-      <c r="O60" s="57"/>
-      <c r="P60" s="57"/>
-      <c r="Q60" s="57"/>
-      <c r="R60" s="57"/>
-      <c r="S60" s="57"/>
-      <c r="T60" s="57"/>
-      <c r="U60" s="57"/>
-      <c r="V60" s="57"/>
-      <c r="W60" s="57"/>
-      <c r="X60" s="57"/>
-      <c r="Y60" s="57"/>
-      <c r="Z60" s="57"/>
-      <c r="AA60" s="57"/>
+      <c r="A60" s="60"/>
+      <c r="B60" s="61"/>
+      <c r="C60" s="62" t="s">
+        <v>57</v>
+      </c>
+      <c r="D60" s="62"/>
+      <c r="E60" s="62"/>
+      <c r="F60" s="62"/>
+      <c r="G60" s="62"/>
+      <c r="H60" s="62"/>
+      <c r="I60" s="62"/>
+      <c r="J60" s="62"/>
+      <c r="K60" s="62"/>
+      <c r="L60" s="62"/>
+      <c r="M60" s="62"/>
+      <c r="O60" s="58"/>
+      <c r="P60" s="58"/>
+      <c r="Q60" s="58"/>
+      <c r="R60" s="58"/>
+      <c r="S60" s="58"/>
+      <c r="T60" s="58"/>
+      <c r="U60" s="58"/>
+      <c r="V60" s="58"/>
+      <c r="W60" s="58"/>
+      <c r="X60" s="58"/>
+      <c r="Y60" s="58"/>
+      <c r="Z60" s="58"/>
+      <c r="AA60" s="58"/>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A61" s="59"/>
-      <c r="B61" s="60"/>
-      <c r="C61" s="61"/>
-      <c r="D61" s="61"/>
-      <c r="E61" s="61"/>
-      <c r="F61" s="61"/>
-      <c r="G61" s="61"/>
-      <c r="H61" s="61"/>
-      <c r="I61" s="61"/>
-      <c r="J61" s="61"/>
-      <c r="K61" s="61"/>
-      <c r="L61" s="61"/>
-      <c r="M61" s="61"/>
-      <c r="O61" s="57"/>
-      <c r="P61" s="57"/>
-      <c r="Q61" s="57"/>
-      <c r="R61" s="57"/>
-      <c r="S61" s="57"/>
-      <c r="T61" s="57"/>
-      <c r="U61" s="57"/>
-      <c r="V61" s="57"/>
-      <c r="W61" s="57"/>
-      <c r="X61" s="57"/>
-      <c r="Y61" s="57"/>
-      <c r="Z61" s="57"/>
-      <c r="AA61" s="57"/>
+      <c r="A61" s="60"/>
+      <c r="B61" s="61"/>
+      <c r="C61" s="62"/>
+      <c r="D61" s="62"/>
+      <c r="E61" s="62"/>
+      <c r="F61" s="62"/>
+      <c r="G61" s="62"/>
+      <c r="H61" s="62"/>
+      <c r="I61" s="62"/>
+      <c r="J61" s="62"/>
+      <c r="K61" s="62"/>
+      <c r="L61" s="62"/>
+      <c r="M61" s="62"/>
+      <c r="O61" s="58"/>
+      <c r="P61" s="58"/>
+      <c r="Q61" s="58"/>
+      <c r="R61" s="58"/>
+      <c r="S61" s="58"/>
+      <c r="T61" s="58"/>
+      <c r="U61" s="58"/>
+      <c r="V61" s="58"/>
+      <c r="W61" s="58"/>
+      <c r="X61" s="58"/>
+      <c r="Y61" s="58"/>
+      <c r="Z61" s="58"/>
+      <c r="AA61" s="58"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A62" s="62" t="s">
-        <v>57</v>
-      </c>
-      <c r="B62" s="63" t="s">
+      <c r="A62" s="63" t="s">
         <v>58</v>
       </c>
-      <c r="C62" s="63"/>
-      <c r="D62" s="63"/>
-      <c r="E62" s="63"/>
-      <c r="F62" s="63"/>
-      <c r="G62" s="63"/>
-      <c r="H62" s="63"/>
-      <c r="I62" s="63"/>
-      <c r="J62" s="63"/>
-      <c r="K62" s="63"/>
-      <c r="L62" s="63"/>
-      <c r="M62" s="63"/>
-      <c r="O62" s="64"/>
-      <c r="P62" s="64"/>
-      <c r="Q62" s="64"/>
-      <c r="R62" s="64"/>
-      <c r="S62" s="64"/>
-      <c r="T62" s="64"/>
-      <c r="U62" s="64"/>
-      <c r="V62" s="64"/>
-      <c r="W62" s="64"/>
-      <c r="X62" s="64"/>
-      <c r="Y62" s="64"/>
-      <c r="Z62" s="64"/>
-      <c r="AA62" s="64"/>
+      <c r="B62" s="64" t="s">
+        <v>59</v>
+      </c>
+      <c r="C62" s="64"/>
+      <c r="D62" s="64"/>
+      <c r="E62" s="64"/>
+      <c r="F62" s="64"/>
+      <c r="G62" s="64"/>
+      <c r="H62" s="64"/>
+      <c r="I62" s="64"/>
+      <c r="J62" s="64"/>
+      <c r="K62" s="64"/>
+      <c r="L62" s="64"/>
+      <c r="M62" s="64"/>
+      <c r="O62" s="65"/>
+      <c r="P62" s="65"/>
+      <c r="Q62" s="65"/>
+      <c r="R62" s="65"/>
+      <c r="S62" s="65"/>
+      <c r="T62" s="65"/>
+      <c r="U62" s="65"/>
+      <c r="V62" s="65"/>
+      <c r="W62" s="65"/>
+      <c r="X62" s="65"/>
+      <c r="Y62" s="65"/>
+      <c r="Z62" s="65"/>
+      <c r="AA62" s="65"/>
     </row>
     <row r="63" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A63" s="62"/>
-      <c r="B63" s="63"/>
-      <c r="C63" s="63"/>
-      <c r="D63" s="63"/>
-      <c r="E63" s="63"/>
-      <c r="F63" s="63"/>
-      <c r="G63" s="63"/>
-      <c r="H63" s="63"/>
-      <c r="I63" s="63"/>
-      <c r="J63" s="63"/>
-      <c r="K63" s="63"/>
-      <c r="L63" s="63"/>
-      <c r="M63" s="63"/>
-      <c r="O63" s="65"/>
-      <c r="P63" s="65"/>
-      <c r="Q63" s="65"/>
-      <c r="R63" s="65"/>
-      <c r="S63" s="65"/>
-      <c r="T63" s="65"/>
-      <c r="U63" s="65"/>
-      <c r="V63" s="65"/>
-      <c r="W63" s="65"/>
-      <c r="X63" s="65"/>
-      <c r="Y63" s="65"/>
-      <c r="Z63" s="65"/>
-      <c r="AA63" s="65"/>
+      <c r="A63" s="63"/>
+      <c r="B63" s="64"/>
+      <c r="C63" s="64"/>
+      <c r="D63" s="64"/>
+      <c r="E63" s="64"/>
+      <c r="F63" s="64"/>
+      <c r="G63" s="64"/>
+      <c r="H63" s="64"/>
+      <c r="I63" s="64"/>
+      <c r="J63" s="64"/>
+      <c r="K63" s="64"/>
+      <c r="L63" s="64"/>
+      <c r="M63" s="64"/>
+      <c r="O63" s="66"/>
+      <c r="P63" s="66"/>
+      <c r="Q63" s="66"/>
+      <c r="R63" s="66"/>
+      <c r="S63" s="66"/>
+      <c r="T63" s="66"/>
+      <c r="U63" s="66"/>
+      <c r="V63" s="66"/>
+      <c r="W63" s="66"/>
+      <c r="X63" s="66"/>
+      <c r="Y63" s="66"/>
+      <c r="Z63" s="66"/>
+      <c r="AA63" s="66"/>
     </row>
     <row r="64" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O64" s="65"/>
-      <c r="P64" s="65"/>
-      <c r="Q64" s="65"/>
-      <c r="R64" s="65"/>
-      <c r="S64" s="65"/>
-      <c r="T64" s="65"/>
-      <c r="U64" s="65"/>
-      <c r="V64" s="65"/>
-      <c r="W64" s="65"/>
-      <c r="X64" s="65"/>
-      <c r="Y64" s="65"/>
-      <c r="Z64" s="65"/>
-      <c r="AA64" s="65"/>
+      <c r="O64" s="66"/>
+      <c r="P64" s="66"/>
+      <c r="Q64" s="66"/>
+      <c r="R64" s="66"/>
+      <c r="S64" s="66"/>
+      <c r="T64" s="66"/>
+      <c r="U64" s="66"/>
+      <c r="V64" s="66"/>
+      <c r="W64" s="66"/>
+      <c r="X64" s="66"/>
+      <c r="Y64" s="66"/>
+      <c r="Z64" s="66"/>
+      <c r="AA64" s="66"/>
     </row>
     <row r="65" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="O65" s="65"/>
-      <c r="P65" s="65"/>
-      <c r="Q65" s="65"/>
-      <c r="R65" s="65"/>
-      <c r="S65" s="65"/>
-      <c r="T65" s="65"/>
-      <c r="U65" s="65"/>
-      <c r="V65" s="65"/>
-      <c r="W65" s="65"/>
-      <c r="X65" s="65"/>
-      <c r="Y65" s="65"/>
-      <c r="Z65" s="65"/>
-      <c r="AA65" s="65"/>
+      <c r="O65" s="66"/>
+      <c r="P65" s="66"/>
+      <c r="Q65" s="66"/>
+      <c r="R65" s="66"/>
+      <c r="S65" s="66"/>
+      <c r="T65" s="66"/>
+      <c r="U65" s="66"/>
+      <c r="V65" s="66"/>
+      <c r="W65" s="66"/>
+      <c r="X65" s="66"/>
+      <c r="Y65" s="66"/>
+      <c r="Z65" s="66"/>
+      <c r="AA65" s="66"/>
     </row>
     <row r="84" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE84" s="66"/>
+      <c r="AE84" s="67"/>
     </row>
     <row r="85" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE85" s="66"/>
+      <c r="AE85" s="67"/>
     </row>
     <row r="86" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE86" s="66"/>
+      <c r="AE86" s="67"/>
     </row>
     <row r="87" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE87" s="66"/>
+      <c r="AE87" s="67"/>
     </row>
     <row r="88" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE88" s="66"/>
+      <c r="AE88" s="67"/>
     </row>
     <row r="89" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE89" s="66"/>
+      <c r="AE89" s="67"/>
     </row>
     <row r="90" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE90" s="66"/>
+      <c r="AE90" s="67"/>
     </row>
     <row r="91" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE91" s="66"/>
+      <c r="AE91" s="67"/>
     </row>
     <row r="92" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE92" s="66"/>
+      <c r="AE92" s="67"/>
     </row>
     <row r="93" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE93" s="66"/>
+      <c r="AE93" s="67"/>
     </row>
     <row r="94" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE94" s="66"/>
+      <c r="AE94" s="67"/>
     </row>
     <row r="95" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE95" s="66"/>
+      <c r="AE95" s="67"/>
     </row>
     <row r="96" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE96" s="66"/>
+      <c r="AE96" s="67"/>
     </row>
     <row r="97" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE97" s="66"/>
+      <c r="AE97" s="67"/>
     </row>
     <row r="98" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE98" s="66"/>
+      <c r="AE98" s="67"/>
     </row>
     <row r="99" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE99" s="66"/>
+      <c r="AE99" s="67"/>
     </row>
     <row r="100" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE100" s="66"/>
+      <c r="AE100" s="67"/>
     </row>
     <row r="101" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE101" s="66"/>
+      <c r="AE101" s="67"/>
     </row>
     <row r="102" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE102" s="66"/>
+      <c r="AE102" s="67"/>
     </row>
     <row r="103" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE103" s="66"/>
+      <c r="AE103" s="67"/>
     </row>
     <row r="104" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE104" s="66"/>
+      <c r="AE104" s="67"/>
     </row>
     <row r="105" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE105" s="66"/>
+      <c r="AE105" s="67"/>
     </row>
     <row r="106" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE106" s="66"/>
+      <c r="AE106" s="67"/>
     </row>
     <row r="107" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE107" s="66"/>
+      <c r="AE107" s="67"/>
     </row>
     <row r="108" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE108" s="66"/>
+      <c r="AE108" s="67"/>
     </row>
     <row r="109" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE109" s="66"/>
+      <c r="AE109" s="67"/>
     </row>
     <row r="110" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE110" s="66"/>
+      <c r="AE110" s="67"/>
     </row>
     <row r="111" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE111" s="66"/>
+      <c r="AE111" s="67"/>
     </row>
     <row r="112" customFormat="false" ht="18.75" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="AE112" s="66"/>
+      <c r="AE112" s="67"/>
     </row>
   </sheetData>
   <mergeCells count="150">
